--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -28,24 +28,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="minutos_partido" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$175</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$263</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AO$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'minutos_partido'!$A$1:$F$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'minutos_partido'!$A$1:$F$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -26278,7 +26278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27911,8 +27911,788 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Hércules</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Real Madrid Castilla</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Gimnàstic</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Atlético Madrileño</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Sant Andreu</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>CDA Águilas FC</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>CD Teruel</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Juventud Torremolinos CF</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K61"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -27954,6 +28734,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27965,7 +28765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28010,7 +28810,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -28019,7 +28819,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -28029,7 +28829,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -28040,7 +28840,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -28049,17 +28849,17 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Villarreal B</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -28070,7 +28870,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -28079,7 +28879,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -28089,7 +28889,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Villarreal B</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -28098,43 +28898,12 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Primera Federación</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>SD Huesca</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28146,7 +28915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28453,8 +29222,296 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Hércules</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/es-ar/equipo/ce-europa/partidos-resultados/8wr1fkahj2tx6zqk6e1qi4jq5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -28463,6 +29520,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28474,7 +29539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29285,8 +30350,208 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Sofascore</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>La lectura web de statistics del evento 16599931 y events/round/8 no está accesible (19-10-2026)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>No añado métricas ni filas del grupo sin respuesta de la fuente; cobertura de grupo 2 permanece hasta J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Marcador</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>La consulta web de team/2815/events/next/0 no está accesible</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Conservo datos/sofascore.json sin cambios por la regla indicada</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Posesión</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Club 50 %; BeSoccer 49 % para el Zaragoza</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Uso BeSoccer; los tiros coinciden: 9-9 y 3-1 a puerta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Estadísticas del club</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Muchos ceros aparentes: faltas y tarjetas contradicen los eventos; el desglose de tiros no suma</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>No uso esos ceros ni los estimo; bloqueo de tiros de BeSoccer</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Expulsión</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>futboltotal indica roja directa; BeSoccer y Sport Aragón indican doble amarilla en el 82</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Registro Segunda amarilla para P. Ademo; primera amarilla 45; Escudero 14; Ander 73; Pau 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Cambios</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>La ficha oficial entremezcla nombres de los equipos en el 69</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Pau Sans sustituye a Edu Espiau: confirmado por los onces y el resto de sustituciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>No se ha podido acceder a un vídeo reproducible ni verificar sus fotogramas</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Análisis visual pendiente; no se modifica goles_video.csv (partido 0-0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Previa CE Europa</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Futbolme no accesible y calendario completo de BeSoccer no recuperable</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Resultados de Goal contrastados J1-J7 con grupo2_partidos.csv; J8 cuadra con clasificación oficial (6-14 y 7 puntos); pendiente contraste futbolme/BeSoccer solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Grupo 2 PJ</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Cada equipo tiene 7 partidos en grupo2_partidos.csv y 8 en la clasificación J8</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Faltan los diez partidos de J8: no se presenta la cobertura como actualizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Primera expulsión del Zaragoza: Ademo en el 82</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Añadido minuto a tarjetas.csv y salida sin cambio en Python y R; no se añade una sustitución ficticia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D40"/>
+  <autoFilter ref="A1:D50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32651,13 +33916,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="4" t="n">
-        <v>554</v>
+        <v>639</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>4</v>
@@ -32669,10 +33934,10 @@
         <v>8</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -32682,13 +33947,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -32711,13 +33976,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>522</v>
+        <v>612</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>2</v>
@@ -32729,10 +33994,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>261</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -32742,13 +34007,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="D5" s="5" t="n">
-        <v>516</v>
+        <v>606</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -32771,13 +34036,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>511</v>
+        <v>601</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
@@ -32789,10 +34054,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>256</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -32802,13 +34067,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -32827,17 +34092,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Raúl Pereira</t>
+          <t>P. Ademo</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -32856,17 +34121,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>P. Ademo</t>
+          <t>Raúl Pereira</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -32914,31 +34179,33 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Iker Vadillo</t>
+          <t>Óscar Ureña</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="n"/>
+        <v>0.99</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -32947,13 +34214,13 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="D12" s="4" t="n">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -32965,10 +34232,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>286</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13">
@@ -32978,13 +34245,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1</v>
@@ -32996,42 +34263,40 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Óscar Ureña</t>
+          <t>Iker Vadillo</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -33040,13 +34305,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="D15" s="5" t="n">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -33069,13 +34334,13 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
@@ -33098,13 +34363,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>3</v>
@@ -33115,23 +34380,27 @@
       <c r="G17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>H. Barrachina</t>
+          <t>J. Gabilondo</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>163</v>
+        <v>233</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
@@ -33142,23 +34411,25 @@
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>J. Gabilondo</t>
+          <t>H. Barrachina</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -33179,13 +34450,13 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1</v>
@@ -33373,7 +34644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36104,8 +37375,392 @@
         <v>8</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Westerveld</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>J. Gabilondo</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Rubo</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Diego González</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>S. Escudero</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>P. Ademo</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Lucas Terrer</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Rubén Díez</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Edu Espiau</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Marco Sangalli</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>H. Barrachina</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F113"/>
+  <autoFilter ref="A1:F129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36116,7 +37771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -37003,7 +38658,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>«Amarilla» o «Roja».</t>
+          <t>«Amarilla», «Roja» o «Segunda amarilla».</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -37025,49 +38680,49 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Minuto base de la tarjeta; vacío si no se ha recogido. Las expulsiones cierran los minutos jugados, sin descuento.</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-…</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>tiros</t>
+          <t>tarjetas</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-…</t>
         </is>
       </c>
     </row>
@@ -37079,12 +38734,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>tiros_zaragoza</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Tiros totales del Zaragoza.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -37094,7 +38749,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -37106,12 +38761,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>tiros_rival</t>
+          <t>tiros_zaragoza</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Tiros totales del rival.</t>
+          <t>Tiros totales del Zaragoza.</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -37121,7 +38776,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -37133,12 +38788,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>a_puerta_zaragoza</t>
+          <t>tiros_rival</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Tiros a puerta del Zaragoza.</t>
+          <t>Tiros totales del rival.</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -37148,7 +38803,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -37160,12 +38815,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>a_puerta_rival</t>
+          <t>a_puerta_zaragoza</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Tiros a puerta del rival.</t>
+          <t>Tiros a puerta del Zaragoza.</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -37175,7 +38830,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -37187,12 +38842,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>posesion_pct</t>
+          <t>a_puerta_rival</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Posesión del Zaragoza, en %.</t>
+          <t>Tiros a puerta del rival.</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -37202,7 +38857,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -37214,22 +38869,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>completo</t>
+          <t>posesion_pct</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>«si» si a puerta + fuera + bloqueados suman el total; «no» si no cuadra.</t>
+          <t>Posesión del Zaragoza, en %.</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -37241,12 +38896,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Fuente que me quedo para ese partido.</t>
+          <t>«si» si a puerta + fuera + bloqueados suman el total; «no» si no cuadra.</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -37256,7 +38911,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Web del club</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -37268,12 +38923,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>fuente</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Explicación de la comprobación de los tiros.</t>
+          <t>Fuente que me quedo para ese partido.</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -37283,7 +38938,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>9 a puerta y 16 fuera suman 25; no hay bloqueados publicados</t>
+          <t>Web del club</t>
         </is>
       </c>
     </row>
@@ -37295,12 +38950,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Explicación de la comprobación de los tiros.</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -37310,34 +38965,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027…</t>
+          <t>9 a puerta y 16 fuera suman 25; no hay bloqueados publicados</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>estadisticas</t>
+          <t>tiros</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027…</t>
         </is>
       </c>
     </row>
@@ -37349,22 +39004,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>periodo</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>«Partido», «1.ª parte» o «2.ª parte».</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Partido</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -37376,12 +39031,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>metrica</t>
+          <t>periodo</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Nombre de la métrica (posesión, córners, faltas…).</t>
+          <t>«Partido», «1.ª parte» o «2.ª parte».</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -37391,7 +39046,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>posesion_pct</t>
+          <t>Partido</t>
         </is>
       </c>
     </row>
@@ -37403,22 +39058,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>zaragoza</t>
+          <t>metrica</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Valor del Zaragoza.</t>
+          <t>Nombre de la métrica (posesión, córners, faltas…).</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>posesion_pct</t>
         </is>
       </c>
     </row>
@@ -37430,12 +39085,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>valor_rival</t>
+          <t>zaragoza</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Valor del rival.</t>
+          <t>Valor del Zaragoza.</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -37445,7 +39100,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -37457,22 +39112,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>calidad</t>
+          <t>valor_rival</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>«ok» si lo he podido contrastar; otro valor si hay dudas.</t>
+          <t>Valor del rival.</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -37484,12 +39139,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>calidad</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>«ok» si lo he podido contrastar; otro valor si hay dudas.</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -37499,34 +39154,34 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>https://www.besoccer.com/match/real-zaragoza/antequera/20…</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>estadisticas</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://www.besoccer.com/match/real-zaragoza/antequera/20…</t>
         </is>
       </c>
     </row>
@@ -37538,12 +39193,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>evento_sofascore</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Identificador del partido en Sofascore.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -37553,7 +39208,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>16599367</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -37565,22 +39220,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>metrica</t>
+          <t>evento_sofascore</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Métrica. Las que acaban en _ok son aciertos y las que acaban en _total, intentos.</t>
+          <t>Identificador del partido en Sofascore.</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>posesion_pct</t>
+          <t>16599367</t>
         </is>
       </c>
     </row>
@@ -37592,22 +39247,22 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>zaragoza</t>
+          <t>metrica</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Valor del Zaragoza.</t>
+          <t>Métrica. Las que acaban en _ok son aciertos y las que acaban en _total, intentos.</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Número decimal</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>posesion_pct</t>
         </is>
       </c>
     </row>
@@ -37619,12 +39274,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>valor_rival</t>
+          <t>zaragoza</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Valor del rival.</t>
+          <t>Valor del Zaragoza.</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -37634,7 +39289,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>74.0</t>
         </is>
       </c>
     </row>
@@ -37646,49 +39301,49 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>valor_rival</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
+          <t>Valor del rival.</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número decimal</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
+          <t>26.0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>grupo2_partidos</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Jornada de liga.</t>
+          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
         </is>
       </c>
     </row>
@@ -37700,12 +39355,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>evento_sofascore</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Identificador del partido en Sofascore.</t>
+          <t>Jornada de liga.</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -37715,7 +39370,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>16599360</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -37727,22 +39382,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>evento_sofascore</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Fecha del partido (AAAA-MM-DD).</t>
+          <t>Identificador del partido en Sofascore.</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>16599360</t>
         </is>
       </c>
     </row>
@@ -37754,12 +39409,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>equipo</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Equipo al que se refiere la fila (mismo nombre que en la clasificación).</t>
+          <t>Fecha del partido (AAAA-MM-DD).</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -37769,7 +39424,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Algeciras</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -37781,12 +39436,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Rival en ese partido.</t>
+          <t>Equipo al que se refiere la fila (mismo nombre que en la clasificación).</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -37796,7 +39451,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Algeciras</t>
         </is>
       </c>
     </row>
@@ -37808,12 +39463,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Local o Visitante.</t>
+          <t>Rival en ese partido.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -37823,7 +39478,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Cartagena</t>
         </is>
       </c>
     </row>
@@ -37835,22 +39490,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>goles_favor</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Goles del equipo.</t>
+          <t>Local o Visitante.</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Casa</t>
         </is>
       </c>
     </row>
@@ -37862,12 +39517,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>goles_contra</t>
+          <t>goles_favor</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Goles del rival.</t>
+          <t>Goles del equipo.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -37877,7 +39532,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -37889,22 +39544,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>xg</t>
+          <t>goles_contra</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Goles esperados (xG) según Sofascore. Vacío si Sofascore no lo da.</t>
+          <t>Goles del rival.</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Número decimal</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -37916,12 +39571,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>xg_rival</t>
+          <t>xg</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Goles esperados (xG) según Sofascore. Vacío si Sofascore no lo da.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -37931,7 +39586,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
@@ -37943,22 +39598,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ocasiones_claras</t>
+          <t>xg_rival</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Ocasiones claras (big chances).</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Número decimal</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
@@ -37970,12 +39625,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ocasiones_claras_rival</t>
+          <t>ocasiones_claras</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Ocasiones claras (big chances).</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -37985,7 +39640,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -37997,12 +39652,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>tiros</t>
+          <t>ocasiones_claras_rival</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Tiros totales.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -38012,7 +39667,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -38024,12 +39679,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>tiros_rival</t>
+          <t>tiros</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Tiros totales.</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -38039,7 +39694,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -38051,12 +39706,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>tiros_a_puerta</t>
+          <t>tiros_rival</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Tiros entre los tres palos.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -38066,7 +39721,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -38078,12 +39733,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>tiros_a_puerta_rival</t>
+          <t>tiros_a_puerta</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Tiros entre los tres palos.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -38093,7 +39748,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -38105,12 +39760,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>tiros_dentro_area</t>
+          <t>tiros_a_puerta_rival</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Tiros desde dentro del área.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -38120,7 +39775,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -38132,12 +39787,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>tiros_dentro_area_rival</t>
+          <t>tiros_dentro_area</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Tiros desde dentro del área.</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -38147,7 +39802,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -38159,12 +39814,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>posesion_pct</t>
+          <t>tiros_dentro_area_rival</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Posesión, en %.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -38174,7 +39829,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -38186,12 +39841,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>posesion_pct_rival</t>
+          <t>posesion_pct</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Posesión, en %.</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -38201,7 +39856,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -38213,12 +39868,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>pases</t>
+          <t>posesion_pct_rival</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Pases intentados.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -38228,7 +39883,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -38240,12 +39895,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>pases_rival</t>
+          <t>pases</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Pases intentados.</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -38255,7 +39910,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>524</t>
         </is>
       </c>
     </row>
@@ -38267,12 +39922,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>pases_buenos</t>
+          <t>pases_rival</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Pases completados.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -38282,7 +39937,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -38294,12 +39949,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>pases_buenos_rival</t>
+          <t>pases_buenos</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Pases completados.</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -38309,7 +39964,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>459</t>
         </is>
       </c>
     </row>
@@ -38321,12 +39976,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>corners</t>
+          <t>pases_buenos_rival</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Saques de esquina.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -38336,7 +39991,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -38348,12 +40003,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>corners_rival</t>
+          <t>corners</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Saques de esquina.</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -38363,7 +40018,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -38375,12 +40030,12 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>faltas</t>
+          <t>corners_rival</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Faltas cometidas.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -38390,7 +40045,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -38402,12 +40057,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>faltas_rival</t>
+          <t>faltas</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Faltas cometidas.</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -38429,12 +40084,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>amarillas</t>
+          <t>faltas_rival</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Tarjetas amarillas.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -38444,7 +40099,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -38456,12 +40111,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>amarillas_rival</t>
+          <t>amarillas</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Tarjetas amarillas.</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -38471,7 +40126,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -38483,12 +40138,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>rojas</t>
+          <t>amarillas_rival</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Tarjetas rojas.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -38498,7 +40153,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -38510,12 +40165,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>rojas_rival</t>
+          <t>rojas</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Tarjetas rojas.</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -38525,7 +40180,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -38537,12 +40192,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>duelos_ganados_pct</t>
+          <t>rojas_rival</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Duelos ganados, en %.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -38552,7 +40207,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -38564,12 +40219,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>duelos_ganados_pct_rival</t>
+          <t>duelos_ganados_pct</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Duelos ganados, en %.</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -38579,7 +40234,7 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -38591,12 +40246,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>entradas_ultimo_tercio</t>
+          <t>duelos_ganados_pct_rival</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Entradas al último tercio del campo.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -38606,7 +40261,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -38618,12 +40273,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>entradas_ultimo_tercio_rival</t>
+          <t>entradas_ultimo_tercio</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Entradas al último tercio del campo.</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -38633,7 +40288,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -38645,12 +40300,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>recuperaciones</t>
+          <t>entradas_ultimo_tercio_rival</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Recuperaciones de balón.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -38660,7 +40315,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -38672,12 +40327,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>recuperaciones_rival</t>
+          <t>recuperaciones</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Recuperaciones de balón.</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -38687,7 +40342,7 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -38699,12 +40354,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>paradas</t>
+          <t>recuperaciones_rival</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Paradas del portero.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -38714,7 +40369,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -38726,12 +40381,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>paradas_rival</t>
+          <t>paradas</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Paradas del portero.</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -38741,7 +40396,7 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -38753,49 +40408,49 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>paradas_rival</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>clasificacion</t>
+          <t>grupo2_partidos</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>tras_jornada</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Jornada después de la cual se toma la clasificación.</t>
+          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
         </is>
       </c>
     </row>
@@ -38807,12 +40462,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>posicion</t>
+          <t>tras_jornada</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Puesto en la tabla.</t>
+          <t>Jornada después de la cual se toma la clasificación.</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -38822,7 +40477,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -38834,22 +40489,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>equipo</t>
+          <t>posicion</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Equipo.</t>
+          <t>Puesto en la tabla.</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -38861,22 +40516,22 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>pj</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Partidos jugados.</t>
+          <t>Equipo.</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
     </row>
@@ -38888,12 +40543,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pj</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Partidos ganados.</t>
+          <t>Partidos jugados.</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -38903,7 +40558,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -38915,12 +40570,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Partidos empatados.</t>
+          <t>Partidos ganados.</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -38930,7 +40585,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -38942,12 +40597,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Partidos perdidos.</t>
+          <t>Partidos empatados.</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -38957,7 +40612,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -38969,12 +40624,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>gf</t>
+          <t>p</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Goles a favor.</t>
+          <t>Partidos perdidos.</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -38984,7 +40639,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -38996,12 +40651,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>gc</t>
+          <t>gf</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Goles en contra.</t>
+          <t>Goles a favor.</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -39011,7 +40666,7 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -39023,12 +40678,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>puntos</t>
+          <t>gc</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Puntos.</t>
+          <t>Goles en contra.</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -39038,7 +40693,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -39050,49 +40705,49 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>puntos</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Puntos.</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>proximos</t>
+          <t>clasificacion</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
         </is>
       </c>
     </row>
@@ -39104,22 +40759,22 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>competicion</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Competición.</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Primera Federación</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -39131,12 +40786,12 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>competicion</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Fecha prevista (puede cambiar).</t>
+          <t>Competición.</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -39146,7 +40801,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>Primera Federación</t>
         </is>
       </c>
     </row>
@@ -39158,12 +40813,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>«Casa» o «Fuera».</t>
+          <t>Fecha prevista (puede cambiar).</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -39173,7 +40828,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -39185,12 +40840,12 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>«Casa» o «Fuera».</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -39200,7 +40855,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Fuera</t>
         </is>
       </c>
     </row>
@@ -39212,12 +40867,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -39227,24 +40882,24 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
+          <t>CE Europa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>partidos_rivales</t>
+          <t>proximos</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>equipo</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Equipo del que son los resultados.</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -39254,7 +40909,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
         </is>
       </c>
     </row>
@@ -39266,22 +40921,22 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Equipo del que son los resultados.</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Real Murcia</t>
         </is>
       </c>
     </row>
@@ -39293,22 +40948,22 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Fecha.</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -39320,12 +40975,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Equipo local.</t>
+          <t>Fecha.</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -39335,7 +40990,7 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Hércules</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -39347,12 +41002,12 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>visitante</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Equipo visitante.</t>
+          <t>Equipo local.</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -39362,7 +41017,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Hércules</t>
         </is>
       </c>
     </row>
@@ -39374,22 +41029,22 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>goles_local</t>
+          <t>visitante</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Goles del local.</t>
+          <t>Equipo visitante.</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Real Murcia</t>
         </is>
       </c>
     </row>
@@ -39401,12 +41056,12 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>goles_visitante</t>
+          <t>goles_local</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Goles del visitante.</t>
+          <t>Goles del local.</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -39416,7 +41071,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -39428,49 +41083,49 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>goles_visitante</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Goles del visitante.</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>https://futbolme.com/resultados-directo/equipo/real-murci…</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>incidencias</t>
+          <t>partidos_rivales</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Jornada afectada (0 si afecta a todo el proyecto).</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>https://futbolme.com/resultados-directo/equipo/real-murci…</t>
         </is>
       </c>
     </row>
@@ -39482,22 +41137,22 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Dato o tabla afectada.</t>
+          <t>Jornada afectada (0 si afecta a todo el proyecto).</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -39509,12 +41164,12 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>problema</t>
+          <t>campo</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Qué no cuadra.</t>
+          <t>Dato o tabla afectada.</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -39524,7 +41179,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>No hay datos públicos fiables de coordenadas, tracking, d…</t>
+          <t>Cobertura</t>
         </is>
       </c>
     </row>
@@ -39536,12 +41191,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>problema</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Qué he hecho con ello.</t>
+          <t>Qué no cuadra.</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -39551,24 +41206,24 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>No se estiman ni se rellenan</t>
+          <t>No hay datos públicos fiables de coordenadas, tracking, d…</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>goles_video</t>
+          <t>incidencias</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>gol_id</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Jornada y número de gol del partido (6-02 = segundo gol de la J6).</t>
+          <t>Qué he hecho con ello.</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -39578,7 +41233,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>1-01</t>
+          <t>No se estiman ni se rellenan</t>
         </is>
       </c>
     </row>
@@ -39590,22 +41245,22 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>gol_id</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Jornada y número de gol del partido (6-02 = segundo gol de la J6).</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-01</t>
         </is>
       </c>
     </row>
@@ -39617,12 +41272,12 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Jornada de liga.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -39644,22 +41299,22 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>Jornada de liga.</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -39671,12 +41326,12 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>«Casa» o «Fuera».</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -39686,7 +41341,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
     </row>
@@ -39698,12 +41353,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>sentido</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>«Favor» o «Contra».</t>
+          <t>«Casa» o «Fuera».</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -39713,7 +41368,7 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Contra</t>
+          <t>Fuera</t>
         </is>
       </c>
     </row>
@@ -39725,12 +41380,12 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>sentido</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Minuto en texto, con el descuento (45+7).</t>
+          <t>«Favor» o «Contra».</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -39740,7 +41395,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Contra</t>
         </is>
       </c>
     </row>
@@ -39752,12 +41407,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>marcador</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Resultado justo después del gol, siempre Zaragoza-rival.</t>
+          <t>Minuto en texto, con el descuento (45+7).</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -39767,7 +41422,7 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -39779,12 +41434,12 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>goleador</t>
+          <t>marcador</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Quién marca.</t>
+          <t>Resultado justo después del gol, siempre Zaragoza-rival.</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -39794,7 +41449,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Sinan Bakis</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
@@ -39806,12 +41461,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>asistencia</t>
+          <t>goleador</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Quién da el último pase, si consta.</t>
+          <t>Quién marca.</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -39821,7 +41476,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>Sinan Bakis</t>
         </is>
       </c>
     </row>
@@ -39833,12 +41488,12 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>inicio</t>
+          <t>asistencia</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Cómo empieza la jugada: ataque posicional, transición, balón parado, penalti o sin dato.</t>
+          <t>Quién da el último pase, si consta.</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -39848,7 +41503,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>balon_parado</t>
+          <t>Jaume Jardí</t>
         </is>
       </c>
     </row>
@@ -39860,12 +41515,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>detalle_inicio</t>
+          <t>inicio</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>La misma idea en una frase corta.</t>
+          <t>Cómo empieza la jugada: ataque posicional, transición, balón parado, penalti o sin dato.</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -39875,7 +41530,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>falta lateral</t>
+          <t>balon_parado</t>
         </is>
       </c>
     </row>
@@ -39887,12 +41542,12 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>carril</t>
+          <t>detalle_inicio</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Izquierda, centro o derecha DEL EQUIPO QUE ATACA.</t>
+          <t>La misma idea en una frase corta.</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -39902,7 +41557,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>derecha</t>
+          <t>falta lateral</t>
         </is>
       </c>
     </row>
@@ -39914,12 +41569,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>ultimo_pase</t>
+          <t>carril</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Tipo de último pase: centro lateral, pase atrás, pase raso por dentro, al espacio, rechace, córner, falta…</t>
+          <t>Izquierda, centro o derecha DEL EQUIPO QUE ATACA.</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -39929,7 +41584,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>falta_lateral</t>
+          <t>derecha</t>
         </is>
       </c>
     </row>
@@ -39941,12 +41596,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>zona_remate</t>
+          <t>ultimo_pase</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Zona del último toque: área pequeña, área grande (centro o lateral), fuera del área o penalti.</t>
+          <t>Tipo de último pase: centro lateral, pase atrás, pase raso por dentro, al espacio, rechace, córner, falta…</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -39956,7 +41611,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>area_pequena</t>
+          <t>falta_lateral</t>
         </is>
       </c>
     </row>
@@ -39968,12 +41623,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>remate</t>
+          <t>zona_remate</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Con qué se remata: pie, cabeza o propia puerta.</t>
+          <t>Zona del último toque: área pequeña, área grande (centro o lateral), fuera del área o penalti.</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -39983,7 +41638,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>sin_dato</t>
+          <t>area_pequena</t>
         </is>
       </c>
     </row>
@@ -39995,12 +41650,12 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>revision_fvs</t>
+          <t>remate</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Si se ve una revisión en el monitor (FVS).</t>
+          <t>Con qué se remata: pie, cabeza o propia puerta.</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -40010,7 +41665,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>no_se_ve</t>
+          <t>sin_dato</t>
         </is>
       </c>
     </row>
@@ -40022,22 +41677,22 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>defensores_area</t>
+          <t>revision_fvs</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Defensores dentro del área en el momento del último pase, solo si se ven todos.</t>
+          <t>Si se ve una revisión en el monitor (FVS).</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>no_se_ve</t>
         </is>
       </c>
     </row>
@@ -40049,12 +41704,12 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>atacantes_area</t>
+          <t>defensores_area</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Atacantes dentro del área en ese mismo momento.</t>
+          <t>Defensores dentro del área en el momento del último pase, solo si se ven todos.</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -40064,7 +41719,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -40076,12 +41731,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>tiro_x</t>
+          <t>atacantes_area</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Posición estimada del remate, en metros hacia la portería rival (0 a 105).</t>
+          <t>Atacantes dentro del área en ese mismo momento.</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -40091,7 +41746,7 @@
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -40103,12 +41758,12 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>tiro_y</t>
+          <t>tiro_x</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Posición estimada del remate, en metros desde la banda derecha del que ataca (0 a 68).</t>
+          <t>Posición estimada del remate, en metros hacia la portería rival (0 a 105).</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -40118,7 +41773,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -40130,12 +41785,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>pase_x</t>
+          <t>tiro_y</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Posición estimada del último pase (x).</t>
+          <t>Posición estimada del remate, en metros desde la banda derecha del que ataca (0 a 68).</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -40145,7 +41800,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -40157,12 +41812,12 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>pase_y</t>
+          <t>pase_x</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Posición estimada del último pase (y).</t>
+          <t>Posición estimada del último pase (x).</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -40172,7 +41827,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -40184,22 +41839,22 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>segundos_video</t>
+          <t>pase_y</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Dónde está la jugada en el resumen, en segundos.</t>
+          <t>Posición estimada del último pase (y).</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -40211,12 +41866,12 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>confianza</t>
+          <t>segundos_video</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Alta, media o baja: lo bien que se ve la jugada.</t>
+          <t>Dónde está la jugada en el resumen, en segundos.</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -40226,7 +41881,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>17-26</t>
         </is>
       </c>
     </row>
@@ -40238,12 +41893,12 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>confianza</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Lo que se ve en el vídeo, explicado en una o dos frases.</t>
+          <t>Alta, media o baja: lo bien que se ve la jugada.</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -40253,34 +41908,34 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Falta desde la derecha del ataque del Nàstic. El balón ca…</t>
+          <t>media</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>resumenes_youtube</t>
+          <t>goles_video</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Lo que se ve en el vídeo, explicado en una o dos frases.</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Falta desde la derecha del ataque del Nàstic. El balón ca…</t>
         </is>
       </c>
     </row>
@@ -40292,12 +41947,12 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -40319,22 +41974,22 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -40346,12 +42001,12 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Canal de YouTube que publica el resumen.</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -40361,7 +42016,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Real Federación Española Fútbol</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
     </row>
@@ -40373,12 +42028,12 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>canal</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Título del vídeo.</t>
+          <t>Canal de YouTube que publica el resumen.</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -40388,7 +42043,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Resumen #PrimeraFederación | Gimnàstic 2-0 Real Zaragoza …</t>
+          <t>Real Federación Española Fútbol</t>
         </is>
       </c>
     </row>
@@ -40400,12 +42055,12 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>duracion</t>
+          <t>titulo</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Duración (minutos:segundos).</t>
+          <t>Título del vídeo.</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -40415,7 +42070,7 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>4:03</t>
+          <t>Resumen #PrimeraFederación | Gimnàstic 2-0 Real Zaragoza …</t>
         </is>
       </c>
     </row>
@@ -40427,12 +42082,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>duracion</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Enlace al vídeo.</t>
+          <t>Duración (minutos:segundos).</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -40442,24 +42097,24 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=psvkPAyTRhk</t>
+          <t>4:03</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>jugadores</t>
+          <t>resumenes_youtube</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>jugador</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Jugador.</t>
+          <t>Enlace al vídeo.</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -40469,7 +42124,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>https://www.youtube.com/watch?v=psvkPAyTRhk</t>
         </is>
       </c>
     </row>
@@ -40481,22 +42136,22 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>partidos</t>
+          <t>jugador</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Partidos jugados.</t>
+          <t>Jugador.</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Jaume Jardí</t>
         </is>
       </c>
     </row>
@@ -40508,12 +42163,12 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>titularidades</t>
+          <t>partidos</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Partidos como titular.</t>
+          <t>Partidos jugados.</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -40523,7 +42178,7 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -40535,12 +42190,12 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>minutos</t>
+          <t>titularidades</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Minutos jugados, sin contar el descuento.</t>
+          <t>Partidos como titular.</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -40550,7 +42205,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -40562,12 +42217,12 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>goles</t>
+          <t>minutos</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Goles.</t>
+          <t>Minutos jugados, sin contar el descuento.</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -40577,7 +42232,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>639</t>
         </is>
       </c>
     </row>
@@ -40589,12 +42244,12 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>asistencias</t>
+          <t>goles</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Asistencias (solo las que constan).</t>
+          <t>Goles.</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -40616,12 +42271,12 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>participaciones_con_minutos</t>
+          <t>asistencias</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Goles + asistencias.</t>
+          <t>Asistencias (solo las que constan).</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -40631,7 +42286,7 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -40643,22 +42298,22 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>participaciones_por_90</t>
+          <t>participaciones_con_minutos</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Goles + asistencias por cada 90 minutos jugados.</t>
+          <t>Goles + asistencias.</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Número decimal</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -40670,39 +42325,39 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>minutos_por_participacion</t>
+          <t>participaciones_por_90</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Minutos que tarda de media en participar en un gol. Vacío si no ha participado en ninguno.</t>
+          <t>Goles + asistencias por cada 90 minutos jugados.</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Número decimal</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>1.13</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>minutos_partido</t>
+          <t>jugadores</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>minutos_por_participacion</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Minutos que tarda de media en participar en un gol. Vacío si no ha participado en ninguno.</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -40712,7 +42367,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -40724,22 +42379,22 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>jugador</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Jugador.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Westerveld</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -40751,12 +42406,12 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>rol</t>
+          <t>jugador</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>«Titular» o «Suplente».</t>
+          <t>Jugador.</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -40766,7 +42421,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Westerveld</t>
         </is>
       </c>
     </row>
@@ -40778,22 +42433,22 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>entra</t>
+          <t>rol</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Minuto en el que entra (0 si es titular).</t>
+          <t>«Titular» o «Suplente».</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -40805,12 +42460,12 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>sale</t>
+          <t>entra</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Minuto en el que sale (90 si acaba el partido).</t>
+          <t>Minuto en el que entra (0 si es titular).</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -40820,7 +42475,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -40832,27 +42487,54 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>Minuto en el que sale (90 si acaba el partido).</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>Número entero</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>minutos_partido</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
           <t>minutos</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>Minutos jugados.</t>
         </is>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D176" s="4" t="inlineStr">
         <is>
           <t>Número entero</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E176" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E175"/>
+  <autoFilter ref="A1:E176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40863,7 +42545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41251,8 +42933,53 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Primera Federación</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -41261,6 +42988,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42459,7 +44187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43639,8 +45367,173 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Westerveld</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>J. Gabilondo</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Rubo</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Diego González</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>S. Escudero</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>P. Ademo</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Lucas Terrer</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Rubén Díez</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Edu Espiau</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C78"/>
+  <autoFilter ref="A1:C89"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -43719,6 +45612,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43730,7 +45634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44572,8 +46476,123 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Marco Sangalli</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>S. Escudero</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Rubén Díez</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Edu Espiau</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>H. Barrachina</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-8-real-murcia-cf-vs-real-zaragoza-3920</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -44610,6 +46629,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44621,13 +46645,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -44651,6 +46676,11 @@
           <t>fuente_url</t>
         </is>
       </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>minuto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -44671,6 +46701,7 @@
           <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-primera-division-rfef-group-2-2026-08-30</t>
         </is>
       </c>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -44691,6 +46722,7 @@
           <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-primera-division-rfef-group-2-2026-08-30</t>
         </is>
       </c>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -44711,6 +46743,7 @@
           <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-primera-division-rfef-group-2-2026-08-30</t>
         </is>
       </c>
+      <c r="E4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -44731,6 +46764,7 @@
           <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-primera-division-rfef-group-2-2026-08-30</t>
         </is>
       </c>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -44751,6 +46785,7 @@
           <t>https://futboltotal.futbol/partido/gimnastic-vs-zaragoza-primera-division-rfef-group-2-2026-08-30</t>
         </is>
       </c>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -44771,6 +46806,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-antequera-primera-division-rfef-group-2-2026-09-06</t>
         </is>
       </c>
+      <c r="E7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -44791,6 +46827,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-antequera-primera-division-rfef-group-2-2026-09-06</t>
         </is>
       </c>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -44811,6 +46848,7 @@
           <t>https://futboltotal.futbol/partido/juventud-torremolinos-vs-zaragoza-primera-division-rfef-group-2-2026-09-13</t>
         </is>
       </c>
+      <c r="E9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -44831,6 +46869,7 @@
           <t>https://futboltotal.futbol/partido/juventud-torremolinos-vs-zaragoza-primera-division-rfef-group-2-2026-09-13</t>
         </is>
       </c>
+      <c r="E10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -44851,6 +46890,7 @@
           <t>https://futboltotal.futbol/partido/juventud-torremolinos-vs-zaragoza-primera-division-rfef-group-2-2026-09-13</t>
         </is>
       </c>
+      <c r="E11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -44871,6 +46911,7 @@
           <t>https://futboltotal.futbol/partido/juventud-torremolinos-vs-zaragoza-primera-division-rfef-group-2-2026-09-13</t>
         </is>
       </c>
+      <c r="E12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -44891,6 +46932,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-fc-cartagena-primera-division-rfef-group-2-2026-09-20</t>
         </is>
       </c>
+      <c r="E13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -44911,6 +46953,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-fc-cartagena-primera-division-rfef-group-2-2026-09-20</t>
         </is>
       </c>
+      <c r="E14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -44931,6 +46974,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -44951,6 +46995,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -44971,6 +47016,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -44991,6 +47037,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -45011,6 +47058,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -45031,6 +47079,7 @@
           <t>https://futboltotal.futbol/partido/ibiza-vs-zaragoza-primera-division-rfef-group-2-2026-09-27</t>
         </is>
       </c>
+      <c r="E20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -45051,6 +47100,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-teruel-primera-division-rfef-grupo-2-2026-10-04</t>
         </is>
       </c>
+      <c r="E21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -45071,6 +47121,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-teruel-primera-division-rfef-grupo-2-2026-10-04</t>
         </is>
       </c>
+      <c r="E22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -45091,6 +47142,7 @@
           <t>https://futboltotal.futbol/partido/zaragoza-vs-teruel-primera-division-rfef-grupo-2-2026-10-04</t>
         </is>
       </c>
+      <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -45111,9 +47163,125 @@
           <t>https://futboltotal.futbol/partido/atletico-madrid-ii-vs-zaragoza-primera-division-rfef-grupo-2-2026-10-11</t>
         </is>
       </c>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>S. Escudero</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>P. Ademo</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>P. Ademo</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Segunda amarilla</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:E29"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -45138,6 +47306,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45149,7 +47322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45159,7 +47332,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
@@ -45494,8 +47667,48 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>BeSoccer (tiros contrastados con el club)</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>9 = 3 a puerta + 3 fuera + 3 bloqueados; posesión del club 50 %</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -45504,6 +47717,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45515,11 +47729,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -49160,8 +51374,1310 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>posesion_pct</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>fueras_juego</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>corners</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>tiros</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>tiros_fuera</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>tiros_puerta</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>tiros_bloqueados</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>paradas_publicadas</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>entradas</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>pases</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>393</v>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>pases_completados</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>faltas</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>amarillas</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>rojas</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>posesion_pct</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>fueras_juego</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>corners</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>tiros</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>tiros_fuera</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>tiros_puerta</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>tiros_bloqueados</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>paradas_publicadas</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>entradas</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>pases</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>pases_completados</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>faltas</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>amarillas</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Primera parte</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>rojas</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>posesion_pct</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>fueras_juego</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>corners</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>tiros</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>tiros_fuera</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>tiros_puerta</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>tiros_bloqueados</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>paradas_publicadas</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>entradas</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>pases</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>pases_completados</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>faltas</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>amarillas</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Segunda parte</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>rojas</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/partido/real-murcia/real-zaragoza/202724302</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G117"/>
+  <autoFilter ref="A1:G159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -49279,6 +52795,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'minutos_partido'!$A$1:$F$129</definedName>
   </definedNames>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -30481,12 +30481,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>No se ha podido acceder a un vídeo reproducible ni verificar sus fotogramas</t>
+          <t>El acceso directo de YouTube fallaba; el usuario ha facilitado el archivo del resumen oficial (154,6 s)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Análisis visual pendiente; no se modifica goles_video.csv (partido 0-0)</t>
+          <t>Análisis visual completado el 19-10-2026; no contiene el córner final al larguero; no se modifica goles_video.csv</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33826,8 +33826,41 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Real Federación Española Fútbol</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Resumen #PrimeraFederación | Real Murcia CF 0-0 Real Zaragoza | Jornada 8 | Temporada 2026/2027</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2:35</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Eq-htl0RmVs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -33837,6 +33870,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$E$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AO$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>262</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14">
@@ -812,12 +812,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -7143,8 +7143,992 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B264" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>posesion_pct</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E264" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B265" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>xg</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B266" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>tiros</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E266" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B267" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>tiros_a_puerta</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B268" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>xgot</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E268" s="4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B269" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>tiros_al_palo</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B270" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>tiros_fuera</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E270" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B271" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>tiros_bloqueados</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B272" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>tiros_dentro_area</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E272" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B273" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>tiros_fuera_area</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B274" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>corners</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>pases</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="F275" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B276" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>pases_buenos</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="E276" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>faltas</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B278" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>amarillas</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E278" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>rojas</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B280" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>entradas</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E280" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B281" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>tiros_libres</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F281" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B282" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>faltas_recibidas_ultimo_tercio</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E282" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B283" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>fueras_juego</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F283" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B284" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>saques_banda</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E284" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B285" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>pases_ultimo_tercio</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E285" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B286" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>balones_largos_ok</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E286" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B287" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>balones_largos_total</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F287" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B288" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>centros_ok</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E288" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B289" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>centros_total</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B290" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>duelos_ganados_pct</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E290" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B291" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>desposeido</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B292" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>duelos_suelo_ok</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E292" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B293" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>duelos_suelo_total</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="F293" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B294" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>duelos_aereos_ok</t>
+        </is>
+      </c>
+      <c r="D294" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E294" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B295" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>duelos_aereos_total</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F295" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B296" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>regates_ok</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B297" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>regates_total</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F297" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B298" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>entradas_ganadas_pct</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E298" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B299" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>intercepciones</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F299" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B300" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>recuperaciones</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E300" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B301" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>despejes</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F301" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B302" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>paradas</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B303" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>goles_evitados</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B304" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>saques_meta</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F304" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F263"/>
+  <autoFilter ref="A1:F304"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -7408,6 +8392,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId303"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30366,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>No añado métricas ni filas del grupo sin respuesta de la fuente; cobertura de grupo 2 permanece hasta J7</t>
+          <t>Métricas de Murcia-Zaragoza incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros nueve partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros nueve partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros ocho partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros ocho partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros siete partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros siete partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros seis partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros seis partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros cinco partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros cinco partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros cuatro partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros cuatro partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros tres partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros tres partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera y Gimnàstic-Atlético Madrileño incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros dos partidos</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -31391,7 +31391,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera y Gimnàstic-Atlético Madrileño incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras faltan los otros dos partidos</t>
+          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera y Gimnàstic-Atlético Madrileño y Sant Andreu-Torremolinos incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras falta Real Jaén-Rayo Majadahonda</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -37,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$304</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AO$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AO$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
@@ -8444,7 +8444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO141"/>
+  <dimension ref="A1:AO161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27149,8 +27149,2556 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J142" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M142" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N142" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q142" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R142" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S142" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T142" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="U142" s="4" t="n">
+        <v>355</v>
+      </c>
+      <c r="V142" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="W142" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="X142" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="Y142" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z142" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA142" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB142" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE142" s="4" t="n"/>
+      <c r="AF142" s="4" t="n"/>
+      <c r="AG142" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH142" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI142" s="4" t="n"/>
+      <c r="AJ142" s="4" t="n"/>
+      <c r="AK142" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL142" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AM142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="N143" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q143" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="R143" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="S143" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="T143" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="U143" s="5" t="n">
+        <v>448</v>
+      </c>
+      <c r="V143" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="W143" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="X143" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="Y143" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z143" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA143" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB143" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" s="5" t="n"/>
+      <c r="AF143" s="5" t="n"/>
+      <c r="AG143" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH143" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI143" s="5" t="n"/>
+      <c r="AJ143" s="5" t="n"/>
+      <c r="AK143" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL143" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO143" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N144" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O144" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R144" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S144" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T144" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="U144" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="V144" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="W144" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="X144" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="Y144" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA144" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB144" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC144" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD144" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG144" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH144" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI144" s="4" t="n"/>
+      <c r="AJ144" s="4" t="n"/>
+      <c r="AK144" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL144" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN144" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO144" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N145" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="O145" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P145" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R145" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="S145" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="T145" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="U145" s="5" t="n">
+        <v>356</v>
+      </c>
+      <c r="V145" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="W145" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="X145" s="5" t="n">
+        <v>374</v>
+      </c>
+      <c r="Y145" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z145" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA145" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB145" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC145" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD145" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG145" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AH145" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI145" s="5" t="n"/>
+      <c r="AJ145" s="5" t="n"/>
+      <c r="AK145" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AL145" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO145" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>CDA Águilas FC</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O146" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P146" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q146" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R146" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S146" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="T146" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="U146" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="V146" s="4" t="n">
+        <v>465</v>
+      </c>
+      <c r="W146" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="X146" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="Y146" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z146" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA146" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB146" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC146" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE146" s="4" t="n"/>
+      <c r="AF146" s="4" t="n"/>
+      <c r="AG146" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH146" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI146" s="4" t="n"/>
+      <c r="AJ146" s="4" t="n"/>
+      <c r="AK146" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AL146" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AM146" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN146" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>CDA Águilas FC</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N147" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O147" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P147" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q147" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R147" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="S147" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="T147" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="U147" s="5" t="n">
+        <v>465</v>
+      </c>
+      <c r="V147" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="W147" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="X147" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="Y147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z147" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA147" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB147" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE147" s="5" t="n"/>
+      <c r="AF147" s="5" t="n"/>
+      <c r="AG147" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH147" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI147" s="5" t="n"/>
+      <c r="AJ147" s="5" t="n"/>
+      <c r="AK147" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="AL147" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="AM147" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO147" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>CD Teruel</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K148" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N148" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O148" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q148" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R148" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S148" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="T148" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U148" s="4" t="n">
+        <v>563</v>
+      </c>
+      <c r="V148" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="W148" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="X148" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="Y148" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA148" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB148" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE148" s="4" t="n"/>
+      <c r="AF148" s="4" t="n"/>
+      <c r="AG148" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH148" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI148" s="4" t="n"/>
+      <c r="AJ148" s="4" t="n"/>
+      <c r="AK148" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL148" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AM148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO148" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>CD Teruel</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M149" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N149" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="O149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P149" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q149" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R149" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S149" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="T149" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="U149" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="V149" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="W149" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="X149" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z149" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA149" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB149" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE149" s="5" t="n"/>
+      <c r="AF149" s="5" t="n"/>
+      <c r="AG149" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH149" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI149" s="5" t="n"/>
+      <c r="AJ149" s="5" t="n"/>
+      <c r="AK149" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL149" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AM149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN149" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B150" s="4" t="n">
+        <v>16599924</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Hércules</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J150" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N150" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O150" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R150" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S150" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T150" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="U150" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="V150" s="4" t="n">
+        <v>413</v>
+      </c>
+      <c r="W150" s="4" t="n">
+        <v>368</v>
+      </c>
+      <c r="X150" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="Y150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z150" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA150" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB150" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC150" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD150" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG150" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AH150" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI150" s="4" t="n"/>
+      <c r="AJ150" s="4" t="n"/>
+      <c r="AK150" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL150" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN150" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO150" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>16599924</v>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Hércules</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N151" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q151" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R151" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S151" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T151" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U151" s="5" t="n">
+        <v>413</v>
+      </c>
+      <c r="V151" s="5" t="n">
+        <v>440</v>
+      </c>
+      <c r="W151" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="X151" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="Y151" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA151" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB151" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC151" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD151" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AH151" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI151" s="5" t="n"/>
+      <c r="AJ151" s="5" t="n"/>
+      <c r="AK151" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AL151" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM151" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO151" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>16599937</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>Real Madrid Castilla</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N152" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O152" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P152" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q152" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R152" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S152" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="T152" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="U152" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="V152" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="W152" s="4" t="n">
+        <v>496</v>
+      </c>
+      <c r="X152" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="Y152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z152" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA152" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB152" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD152" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE152" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG152" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AH152" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI152" s="4" t="n"/>
+      <c r="AJ152" s="4" t="n"/>
+      <c r="AK152" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL152" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN152" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>16599937</v>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>Real Madrid Castilla</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M153" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N153" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O153" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P153" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q153" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R153" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="S153" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="T153" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U153" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="V153" s="5" t="n">
+        <v>555</v>
+      </c>
+      <c r="W153" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="X153" s="5" t="n">
+        <v>496</v>
+      </c>
+      <c r="Y153" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA153" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB153" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC153" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AH153" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI153" s="5" t="n"/>
+      <c r="AJ153" s="5" t="n"/>
+      <c r="AK153" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL153" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM153" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO153" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B154" s="4" t="n">
+        <v>16599934</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>Gimnàstic</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Atlético Madrileño</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N154" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O154" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P154" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R154" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S154" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T154" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="U154" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="V154" s="4" t="n">
+        <v>585</v>
+      </c>
+      <c r="W154" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="X154" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="Y154" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z154" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA154" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB154" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC154" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD154" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE154" s="4" t="n"/>
+      <c r="AF154" s="4" t="n"/>
+      <c r="AG154" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH154" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI154" s="4" t="n"/>
+      <c r="AJ154" s="4" t="n"/>
+      <c r="AK154" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL154" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AM154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO154" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>16599934</v>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Atlético Madrileño</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Gimnàstic</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N155" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q155" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R155" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S155" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="T155" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="U155" s="5" t="n">
+        <v>585</v>
+      </c>
+      <c r="V155" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="W155" s="5" t="n">
+        <v>501</v>
+      </c>
+      <c r="X155" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="Y155" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA155" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB155" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD155" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE155" s="5" t="n"/>
+      <c r="AF155" s="5" t="n"/>
+      <c r="AG155" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH155" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI155" s="5" t="n"/>
+      <c r="AJ155" s="5" t="n"/>
+      <c r="AK155" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL155" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AM155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>16599940</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Sant Andreu</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Juventud Torremolinos CF</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L156" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M156" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O156" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P156" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q156" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="R156" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S156" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T156" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="U156" s="4" t="n">
+        <v>444</v>
+      </c>
+      <c r="V156" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="W156" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="X156" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="Y156" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z156" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA156" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB156" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD156" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE156" s="4" t="n"/>
+      <c r="AF156" s="4" t="n"/>
+      <c r="AG156" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH156" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI156" s="4" t="n"/>
+      <c r="AJ156" s="4" t="n"/>
+      <c r="AK156" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL156" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM156" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN156" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO156" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>16599940</v>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Juventud Torremolinos CF</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Sant Andreu</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M157" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N157" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O157" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P157" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q157" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R157" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="S157" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T157" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U157" s="5" t="n">
+        <v>424</v>
+      </c>
+      <c r="V157" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="W157" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="X157" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="Y157" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z157" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA157" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB157" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC157" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE157" s="5" t="n"/>
+      <c r="AF157" s="5" t="n"/>
+      <c r="AG157" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH157" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI157" s="5" t="n"/>
+      <c r="AJ157" s="5" t="n"/>
+      <c r="AK157" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL157" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AM157" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN157" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO157" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B158" s="4" t="n">
+        <v>16599928</v>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L158" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M158" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q158" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R158" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S158" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T158" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="U158" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="V158" s="4" t="n">
+        <v>421</v>
+      </c>
+      <c r="W158" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="X158" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="Y158" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z158" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA158" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB158" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC158" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD158" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE158" s="4" t="n"/>
+      <c r="AF158" s="4" t="n"/>
+      <c r="AG158" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AH158" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI158" s="4" t="n"/>
+      <c r="AJ158" s="4" t="n"/>
+      <c r="AK158" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL158" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AM158" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>16599928</v>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N159" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O159" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q159" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="R159" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S159" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="T159" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="U159" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="V159" s="5" t="n">
+        <v>354</v>
+      </c>
+      <c r="W159" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="X159" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="Y159" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z159" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA159" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB159" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC159" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD159" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE159" s="5" t="n"/>
+      <c r="AF159" s="5" t="n"/>
+      <c r="AG159" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH159" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI159" s="5" t="n"/>
+      <c r="AJ159" s="5" t="n"/>
+      <c r="AK159" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL159" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN159" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO159" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B160" s="4" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N160" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q160" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R160" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S160" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T160" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="U160" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="V160" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="W160" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="X160" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="Y160" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z160" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA160" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB160" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC160" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD160" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG160" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AH160" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AI160" s="4" t="n"/>
+      <c r="AJ160" s="4" t="n"/>
+      <c r="AK160" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL160" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM160" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO160" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>16599931</v>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K161" s="5" t="n"/>
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N161" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O161" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q161" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R161" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S161" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T161" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U161" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="V161" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="W161" s="5" t="n">
+        <v>302</v>
+      </c>
+      <c r="X161" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="Y161" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z161" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA161" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB161" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC161" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD161" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AH161" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI161" s="5" t="n"/>
+      <c r="AJ161" s="5" t="n"/>
+      <c r="AK161" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL161" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN161" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO161" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO141"/>
+  <autoFilter ref="A1:AO161"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO3" r:id="rId2"/>
@@ -27292,6 +29840,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO161" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31391,7 +33959,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Métricas de Murcia-Zaragoza y Cartagena-Europa y Alcorcón-Huesca y Águilas-Ibiza y Villarreal B-Teruel y Algeciras-Hércules y Castilla-Antequera y Gimnàstic-Atlético Madrileño y Sant Andreu-Torremolinos incorporadas el 20-10-2026 mediante capturas de Sofascore facilitadas por el usuario; comparación del grupo con corte común J7 mientras falta Real Jaén-Rayo Majadahonda</t>
+          <t>Resuelto el 20-10-2026: J8 completa mediante capturas y texto de Sofascore aportados por el usuario. 80 partidos en grupo2_partidos.csv; 77 con xG por tres ausencias antiguas.</t>
         </is>
       </c>
     </row>
@@ -31551,7 +34119,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Faltan los diez partidos de J8: no se presenta la cobertura como actualizada</t>
+          <t>Resuelto el 20-10-2026: J8 completa mediante capturas y texto de Sofascore aportados por el usuario. 80 partidos en grupo2_partidos.csv; 77 con xG por tres ausencias antiguas.</t>
         </is>
       </c>
     </row>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -28,7 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="minutos_partido" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$89</definedName>
@@ -37,11 +37,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$304</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AO$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AQ$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -8444,7 +8444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO161"/>
+  <dimension ref="A1:AQ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8488,6 +8488,8 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col width="60" customWidth="1" min="41" max="41"/>
+    <col width="60" customWidth="1" min="42" max="42"/>
+    <col width="60" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8696,6 +8698,16 @@
           <t>fuente_url</t>
         </is>
       </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>fuente_xg</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>nota_xg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -8827,6 +8839,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
         </is>
       </c>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
+        </is>
+      </c>
+      <c r="AQ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -8958,6 +8976,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
         </is>
       </c>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
+        </is>
+      </c>
+      <c r="AQ3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -9081,6 +9105,8 @@
           <t>https://www.sofascore.com/api/v1/event/16599365/statistics</t>
         </is>
       </c>
+      <c r="AP4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -9204,6 +9230,8 @@
           <t>https://www.sofascore.com/api/v1/event/16599365/statistics</t>
         </is>
       </c>
+      <c r="AP5" s="5" t="n"/>
+      <c r="AQ5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -9335,6 +9363,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599366/statistics</t>
         </is>
       </c>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599366/statistics</t>
+        </is>
+      </c>
+      <c r="AQ6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -9466,6 +9500,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599366/statistics</t>
         </is>
       </c>
+      <c r="AP7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599366/statistics</t>
+        </is>
+      </c>
+      <c r="AQ7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -9597,6 +9637,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599364/statistics</t>
         </is>
       </c>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599364/statistics</t>
+        </is>
+      </c>
+      <c r="AQ8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -9728,6 +9774,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599364/statistics</t>
         </is>
       </c>
+      <c r="AP9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599364/statistics</t>
+        </is>
+      </c>
+      <c r="AQ9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -9863,6 +9915,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599362/statistics</t>
         </is>
       </c>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599362/statistics</t>
+        </is>
+      </c>
+      <c r="AQ10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -9998,6 +10056,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599362/statistics</t>
         </is>
       </c>
+      <c r="AP11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599362/statistics</t>
+        </is>
+      </c>
+      <c r="AQ11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -10129,6 +10193,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599361/statistics</t>
         </is>
       </c>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599361/statistics</t>
+        </is>
+      </c>
+      <c r="AQ12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -10260,6 +10330,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599361/statistics</t>
         </is>
       </c>
+      <c r="AP13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599361/statistics</t>
+        </is>
+      </c>
+      <c r="AQ13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -10395,6 +10471,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599359/statistics</t>
         </is>
       </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599359/statistics</t>
+        </is>
+      </c>
+      <c r="AQ14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -10530,6 +10612,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599359/statistics</t>
         </is>
       </c>
+      <c r="AP15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599359/statistics</t>
+        </is>
+      </c>
+      <c r="AQ15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -10661,6 +10749,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599363/statistics</t>
         </is>
       </c>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599363/statistics</t>
+        </is>
+      </c>
+      <c r="AQ16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -10792,6 +10886,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599363/statistics</t>
         </is>
       </c>
+      <c r="AP17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599363/statistics</t>
+        </is>
+      </c>
+      <c r="AQ17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -10923,6 +11023,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
         </is>
       </c>
+      <c r="AP18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
+        </is>
+      </c>
+      <c r="AQ18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -11054,6 +11160,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
         </is>
       </c>
+      <c r="AP19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599367/statistics</t>
+        </is>
+      </c>
+      <c r="AQ19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -11189,6 +11301,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599368/statistics</t>
         </is>
       </c>
+      <c r="AP20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599368/statistics</t>
+        </is>
+      </c>
+      <c r="AQ20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -11324,6 +11442,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599368/statistics</t>
         </is>
       </c>
+      <c r="AP21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599368/statistics</t>
+        </is>
+      </c>
+      <c r="AQ21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -11358,8 +11482,12 @@
       <c r="H22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
+      <c r="I22" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>2.07</v>
+      </c>
       <c r="K22" s="4" t="n">
         <v>0</v>
       </c>
@@ -11451,6 +11579,16 @@
           <t>https://www.sofascore.com/api/v1/event/16599697/statistics</t>
         </is>
       </c>
+      <c r="AP22" s="4" t="inlineStr">
+        <is>
+          <t>https://scangoal.com/h2h/algeciras-vs-villarreal-b</t>
+        </is>
+      </c>
+      <c r="AQ22" s="4" t="inlineStr">
+        <is>
+          <t>Fuente complementaria; proveedor/modelo de xG no confirmado. No atribuir a Sofascore.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -11485,8 +11623,12 @@
       <c r="H23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
+      <c r="I23" s="5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.93</v>
+      </c>
       <c r="K23" s="5" t="n">
         <v>2</v>
       </c>
@@ -11578,6 +11720,16 @@
           <t>https://www.sofascore.com/api/v1/event/16599697/statistics</t>
         </is>
       </c>
+      <c r="AP23" s="5" t="inlineStr">
+        <is>
+          <t>https://scangoal.com/h2h/algeciras-vs-villarreal-b</t>
+        </is>
+      </c>
+      <c r="AQ23" s="5" t="inlineStr">
+        <is>
+          <t>Fuente complementaria; proveedor/modelo de xG no confirmado. No atribuir a Sofascore.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -11709,6 +11861,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599554/statistics</t>
         </is>
       </c>
+      <c r="AP24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599554/statistics</t>
+        </is>
+      </c>
+      <c r="AQ24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -11840,6 +11998,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599554/statistics</t>
         </is>
       </c>
+      <c r="AP25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599554/statistics</t>
+        </is>
+      </c>
+      <c r="AQ25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -11971,6 +12135,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599684/statistics</t>
         </is>
       </c>
+      <c r="AP26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599684/statistics</t>
+        </is>
+      </c>
+      <c r="AQ26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -12102,6 +12272,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599684/statistics</t>
         </is>
       </c>
+      <c r="AP27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599684/statistics</t>
+        </is>
+      </c>
+      <c r="AQ27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -12233,6 +12409,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599371/statistics</t>
         </is>
       </c>
+      <c r="AP28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599371/statistics</t>
+        </is>
+      </c>
+      <c r="AQ28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -12364,6 +12546,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599371/statistics</t>
         </is>
       </c>
+      <c r="AP29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599371/statistics</t>
+        </is>
+      </c>
+      <c r="AQ29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -12495,6 +12683,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599373/statistics</t>
         </is>
       </c>
+      <c r="AP30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599373/statistics</t>
+        </is>
+      </c>
+      <c r="AQ30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -12626,6 +12820,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599373/statistics</t>
         </is>
       </c>
+      <c r="AP31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599373/statistics</t>
+        </is>
+      </c>
+      <c r="AQ31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -12757,6 +12957,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599713/statistics</t>
         </is>
       </c>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599713/statistics</t>
+        </is>
+      </c>
+      <c r="AQ32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -12888,6 +13094,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599713/statistics</t>
         </is>
       </c>
+      <c r="AP33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599713/statistics</t>
+        </is>
+      </c>
+      <c r="AQ33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -13023,6 +13235,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599388/statistics</t>
         </is>
       </c>
+      <c r="AP34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599388/statistics</t>
+        </is>
+      </c>
+      <c r="AQ34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -13158,6 +13376,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599388/statistics</t>
         </is>
       </c>
+      <c r="AP35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599388/statistics</t>
+        </is>
+      </c>
+      <c r="AQ35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -13289,6 +13513,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599370/statistics</t>
         </is>
       </c>
+      <c r="AP36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599370/statistics</t>
+        </is>
+      </c>
+      <c r="AQ36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -13420,6 +13650,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599370/statistics</t>
         </is>
       </c>
+      <c r="AP37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599370/statistics</t>
+        </is>
+      </c>
+      <c r="AQ37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -13555,6 +13791,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599372/statistics</t>
         </is>
       </c>
+      <c r="AP38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599372/statistics</t>
+        </is>
+      </c>
+      <c r="AQ38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -13690,6 +13932,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599372/statistics</t>
         </is>
       </c>
+      <c r="AP39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599372/statistics</t>
+        </is>
+      </c>
+      <c r="AQ39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -13821,6 +14069,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599399/statistics</t>
         </is>
       </c>
+      <c r="AP40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599399/statistics</t>
+        </is>
+      </c>
+      <c r="AQ40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -13952,6 +14206,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599399/statistics</t>
         </is>
       </c>
+      <c r="AP41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599399/statistics</t>
+        </is>
+      </c>
+      <c r="AQ41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -14083,6 +14343,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599880/statistics</t>
         </is>
       </c>
+      <c r="AP42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599880/statistics</t>
+        </is>
+      </c>
+      <c r="AQ42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -14214,6 +14480,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599880/statistics</t>
         </is>
       </c>
+      <c r="AP43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599880/statistics</t>
+        </is>
+      </c>
+      <c r="AQ43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -14345,6 +14617,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599834/statistics</t>
         </is>
       </c>
+      <c r="AP44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599834/statistics</t>
+        </is>
+      </c>
+      <c r="AQ44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -14476,6 +14754,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599834/statistics</t>
         </is>
       </c>
+      <c r="AP45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599834/statistics</t>
+        </is>
+      </c>
+      <c r="AQ45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -14607,6 +14891,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599856/statistics</t>
         </is>
       </c>
+      <c r="AP46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599856/statistics</t>
+        </is>
+      </c>
+      <c r="AQ46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -14738,6 +15028,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599856/statistics</t>
         </is>
       </c>
+      <c r="AP47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599856/statistics</t>
+        </is>
+      </c>
+      <c r="AQ47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -14869,6 +15165,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599870/statistics</t>
         </is>
       </c>
+      <c r="AP48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599870/statistics</t>
+        </is>
+      </c>
+      <c r="AQ48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -15000,6 +15302,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599870/statistics</t>
         </is>
       </c>
+      <c r="AP49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599870/statistics</t>
+        </is>
+      </c>
+      <c r="AQ49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -15131,6 +15439,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599876/statistics</t>
         </is>
       </c>
+      <c r="AP50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599876/statistics</t>
+        </is>
+      </c>
+      <c r="AQ50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -15262,6 +15576,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599876/statistics</t>
         </is>
       </c>
+      <c r="AP51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599876/statistics</t>
+        </is>
+      </c>
+      <c r="AQ51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -15393,6 +15713,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599882/statistics</t>
         </is>
       </c>
+      <c r="AP52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599882/statistics</t>
+        </is>
+      </c>
+      <c r="AQ52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -15524,6 +15850,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599882/statistics</t>
         </is>
       </c>
+      <c r="AP53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599882/statistics</t>
+        </is>
+      </c>
+      <c r="AQ53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -15655,6 +15987,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599878/statistics</t>
         </is>
       </c>
+      <c r="AP54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599878/statistics</t>
+        </is>
+      </c>
+      <c r="AQ54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -15786,6 +16124,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599878/statistics</t>
         </is>
       </c>
+      <c r="AP55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599878/statistics</t>
+        </is>
+      </c>
+      <c r="AQ55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -15917,6 +16261,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599875/statistics</t>
         </is>
       </c>
+      <c r="AP56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599875/statistics</t>
+        </is>
+      </c>
+      <c r="AQ56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -16048,6 +16398,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599875/statistics</t>
         </is>
       </c>
+      <c r="AP57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599875/statistics</t>
+        </is>
+      </c>
+      <c r="AQ57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -16179,6 +16535,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599877/statistics</t>
         </is>
       </c>
+      <c r="AP58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599877/statistics</t>
+        </is>
+      </c>
+      <c r="AQ58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -16310,6 +16672,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599877/statistics</t>
         </is>
       </c>
+      <c r="AP59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599877/statistics</t>
+        </is>
+      </c>
+      <c r="AQ59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -16441,6 +16809,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599843/statistics</t>
         </is>
       </c>
+      <c r="AP60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599843/statistics</t>
+        </is>
+      </c>
+      <c r="AQ60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -16572,6 +16946,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599843/statistics</t>
         </is>
       </c>
+      <c r="AP61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599843/statistics</t>
+        </is>
+      </c>
+      <c r="AQ61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -16703,6 +17083,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599917/statistics</t>
         </is>
       </c>
+      <c r="AP62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599917/statistics</t>
+        </is>
+      </c>
+      <c r="AQ62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -16834,6 +17220,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599917/statistics</t>
         </is>
       </c>
+      <c r="AP63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599917/statistics</t>
+        </is>
+      </c>
+      <c r="AQ63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -16965,6 +17357,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599918/statistics</t>
         </is>
       </c>
+      <c r="AP64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599918/statistics</t>
+        </is>
+      </c>
+      <c r="AQ64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -17096,6 +17494,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599918/statistics</t>
         </is>
       </c>
+      <c r="AP65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599918/statistics</t>
+        </is>
+      </c>
+      <c r="AQ65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -17227,6 +17631,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599921/statistics</t>
         </is>
       </c>
+      <c r="AP66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599921/statistics</t>
+        </is>
+      </c>
+      <c r="AQ66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -17358,6 +17768,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599921/statistics</t>
         </is>
       </c>
+      <c r="AP67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599921/statistics</t>
+        </is>
+      </c>
+      <c r="AQ67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -17489,6 +17905,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599914/statistics</t>
         </is>
       </c>
+      <c r="AP68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599914/statistics</t>
+        </is>
+      </c>
+      <c r="AQ68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -17620,6 +18042,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599914/statistics</t>
         </is>
       </c>
+      <c r="AP69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599914/statistics</t>
+        </is>
+      </c>
+      <c r="AQ69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -17751,6 +18179,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599916/statistics</t>
         </is>
       </c>
+      <c r="AP70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599916/statistics</t>
+        </is>
+      </c>
+      <c r="AQ70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -17882,6 +18316,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599916/statistics</t>
         </is>
       </c>
+      <c r="AP71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599916/statistics</t>
+        </is>
+      </c>
+      <c r="AQ71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -18013,6 +18453,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599906/statistics</t>
         </is>
       </c>
+      <c r="AP72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599906/statistics</t>
+        </is>
+      </c>
+      <c r="AQ72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -18144,6 +18590,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599906/statistics</t>
         </is>
       </c>
+      <c r="AP73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599906/statistics</t>
+        </is>
+      </c>
+      <c r="AQ73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -18275,6 +18727,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599910/statistics</t>
         </is>
       </c>
+      <c r="AP74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599910/statistics</t>
+        </is>
+      </c>
+      <c r="AQ74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -18406,6 +18864,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599910/statistics</t>
         </is>
       </c>
+      <c r="AP75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599910/statistics</t>
+        </is>
+      </c>
+      <c r="AQ75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -18537,6 +19001,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599912/statistics</t>
         </is>
       </c>
+      <c r="AP76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599912/statistics</t>
+        </is>
+      </c>
+      <c r="AQ76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -18668,6 +19138,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599912/statistics</t>
         </is>
       </c>
+      <c r="AP77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599912/statistics</t>
+        </is>
+      </c>
+      <c r="AQ77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -18803,6 +19279,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599923/statistics</t>
         </is>
       </c>
+      <c r="AP78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599923/statistics</t>
+        </is>
+      </c>
+      <c r="AQ78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -18938,6 +19420,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599923/statistics</t>
         </is>
       </c>
+      <c r="AP79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599923/statistics</t>
+        </is>
+      </c>
+      <c r="AQ79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -19065,6 +19553,12 @@
           <t>https://www.sofascore.com/api/v1/event/16969545/statistics</t>
         </is>
       </c>
+      <c r="AP80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16969545/statistics</t>
+        </is>
+      </c>
+      <c r="AQ80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -19192,6 +19686,12 @@
           <t>https://www.sofascore.com/api/v1/event/16969545/statistics</t>
         </is>
       </c>
+      <c r="AP81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16969545/statistics</t>
+        </is>
+      </c>
+      <c r="AQ81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -19327,6 +19827,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599951/statistics</t>
         </is>
       </c>
+      <c r="AP82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599951/statistics</t>
+        </is>
+      </c>
+      <c r="AQ82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -19462,6 +19968,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599951/statistics</t>
         </is>
       </c>
+      <c r="AP83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599951/statistics</t>
+        </is>
+      </c>
+      <c r="AQ83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -19593,6 +20105,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599962/statistics</t>
         </is>
       </c>
+      <c r="AP84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599962/statistics</t>
+        </is>
+      </c>
+      <c r="AQ84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -19724,6 +20242,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599962/statistics</t>
         </is>
       </c>
+      <c r="AP85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599962/statistics</t>
+        </is>
+      </c>
+      <c r="AQ85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -19859,6 +20383,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599948/statistics</t>
         </is>
       </c>
+      <c r="AP86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599948/statistics</t>
+        </is>
+      </c>
+      <c r="AQ86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -19994,6 +20524,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599948/statistics</t>
         </is>
       </c>
+      <c r="AP87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599948/statistics</t>
+        </is>
+      </c>
+      <c r="AQ87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -20125,6 +20661,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599964/statistics</t>
         </is>
       </c>
+      <c r="AP88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599964/statistics</t>
+        </is>
+      </c>
+      <c r="AQ88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -20256,6 +20798,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599964/statistics</t>
         </is>
       </c>
+      <c r="AP89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599964/statistics</t>
+        </is>
+      </c>
+      <c r="AQ89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -20290,8 +20838,12 @@
       <c r="H90" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
+      <c r="I90" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>2.19</v>
+      </c>
       <c r="K90" s="4" t="n">
         <v>0</v>
       </c>
@@ -20379,6 +20931,16 @@
           <t>https://www.sofascore.com/api/v1/event/16599966/statistics</t>
         </is>
       </c>
+      <c r="AP90" s="4" t="inlineStr">
+        <is>
+          <t>https://nb-bet.com/en/Events/1624476-himnastik-sant-andryu-prognoz-na-match</t>
+        </is>
+      </c>
+      <c r="AQ90" s="4" t="inlineStr">
+        <is>
+          <t>Fuente complementaria; proveedor/modelo de xG no confirmado. No atribuir a Sofascore.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -20413,8 +20975,12 @@
       <c r="H91" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
+      <c r="I91" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.52</v>
+      </c>
       <c r="K91" s="5" t="n">
         <v>2</v>
       </c>
@@ -20502,6 +21068,16 @@
           <t>https://www.sofascore.com/api/v1/event/16599966/statistics</t>
         </is>
       </c>
+      <c r="AP91" s="5" t="inlineStr">
+        <is>
+          <t>https://nb-bet.com/en/Events/1624476-himnastik-sant-andryu-prognoz-na-match</t>
+        </is>
+      </c>
+      <c r="AQ91" s="5" t="inlineStr">
+        <is>
+          <t>Fuente complementaria; proveedor/modelo de xG no confirmado. No atribuir a Sofascore.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -20633,6 +21209,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599960/statistics</t>
         </is>
       </c>
+      <c r="AP92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599960/statistics</t>
+        </is>
+      </c>
+      <c r="AQ92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -20764,6 +21346,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599960/statistics</t>
         </is>
       </c>
+      <c r="AP93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599960/statistics</t>
+        </is>
+      </c>
+      <c r="AQ93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -20895,6 +21483,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599953/statistics</t>
         </is>
       </c>
+      <c r="AP94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599953/statistics</t>
+        </is>
+      </c>
+      <c r="AQ94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -21026,6 +21620,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599953/statistics</t>
         </is>
       </c>
+      <c r="AP95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599953/statistics</t>
+        </is>
+      </c>
+      <c r="AQ95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -21157,6 +21757,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599972/statistics</t>
         </is>
       </c>
+      <c r="AP96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599972/statistics</t>
+        </is>
+      </c>
+      <c r="AQ96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -21288,6 +21894,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599972/statistics</t>
         </is>
       </c>
+      <c r="AP97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599972/statistics</t>
+        </is>
+      </c>
+      <c r="AQ97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -21419,6 +22031,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599969/statistics</t>
         </is>
       </c>
+      <c r="AP98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599969/statistics</t>
+        </is>
+      </c>
+      <c r="AQ98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -21550,6 +22168,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599969/statistics</t>
         </is>
       </c>
+      <c r="AP99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599969/statistics</t>
+        </is>
+      </c>
+      <c r="AQ99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -21685,6 +22309,12 @@
           <t>https://www.sofascore.com/api/v1/event/17118209/statistics</t>
         </is>
       </c>
+      <c r="AP100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/17118209/statistics</t>
+        </is>
+      </c>
+      <c r="AQ100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -21820,6 +22450,12 @@
           <t>https://www.sofascore.com/api/v1/event/17118209/statistics</t>
         </is>
       </c>
+      <c r="AP101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/17118209/statistics</t>
+        </is>
+      </c>
+      <c r="AQ101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -21951,6 +22587,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599792/statistics</t>
         </is>
       </c>
+      <c r="AP102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599792/statistics</t>
+        </is>
+      </c>
+      <c r="AQ102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -22082,6 +22724,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599792/statistics</t>
         </is>
       </c>
+      <c r="AP103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599792/statistics</t>
+        </is>
+      </c>
+      <c r="AQ103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -22217,6 +22865,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599748/statistics</t>
         </is>
       </c>
+      <c r="AP104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599748/statistics</t>
+        </is>
+      </c>
+      <c r="AQ104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -22352,6 +23006,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599748/statistics</t>
         </is>
       </c>
+      <c r="AP105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599748/statistics</t>
+        </is>
+      </c>
+      <c r="AQ105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -22483,6 +23143,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599708/statistics</t>
         </is>
       </c>
+      <c r="AP106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599708/statistics</t>
+        </is>
+      </c>
+      <c r="AQ106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -22614,6 +23280,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599708/statistics</t>
         </is>
       </c>
+      <c r="AP107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599708/statistics</t>
+        </is>
+      </c>
+      <c r="AQ107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -22745,6 +23417,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599734/statistics</t>
         </is>
       </c>
+      <c r="AP108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599734/statistics</t>
+        </is>
+      </c>
+      <c r="AQ108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -22876,6 +23554,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599734/statistics</t>
         </is>
       </c>
+      <c r="AP109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599734/statistics</t>
+        </is>
+      </c>
+      <c r="AQ109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -23007,6 +23691,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599779/statistics</t>
         </is>
       </c>
+      <c r="AP110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599779/statistics</t>
+        </is>
+      </c>
+      <c r="AQ110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -23138,6 +23828,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599779/statistics</t>
         </is>
       </c>
+      <c r="AP111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599779/statistics</t>
+        </is>
+      </c>
+      <c r="AQ111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -23269,6 +23965,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599822/statistics</t>
         </is>
       </c>
+      <c r="AP112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599822/statistics</t>
+        </is>
+      </c>
+      <c r="AQ112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -23400,6 +24102,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599822/statistics</t>
         </is>
       </c>
+      <c r="AP113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599822/statistics</t>
+        </is>
+      </c>
+      <c r="AQ113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -23535,6 +24243,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599763/statistics</t>
         </is>
       </c>
+      <c r="AP114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599763/statistics</t>
+        </is>
+      </c>
+      <c r="AQ114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -23670,6 +24384,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599763/statistics</t>
         </is>
       </c>
+      <c r="AP115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599763/statistics</t>
+        </is>
+      </c>
+      <c r="AQ115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
@@ -23805,6 +24525,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599806/statistics</t>
         </is>
       </c>
+      <c r="AP116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599806/statistics</t>
+        </is>
+      </c>
+      <c r="AQ116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -23940,6 +24666,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599806/statistics</t>
         </is>
       </c>
+      <c r="AP117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599806/statistics</t>
+        </is>
+      </c>
+      <c r="AQ117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -24071,6 +24803,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599724/statistics</t>
         </is>
       </c>
+      <c r="AP118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599724/statistics</t>
+        </is>
+      </c>
+      <c r="AQ118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -24202,6 +24940,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599724/statistics</t>
         </is>
       </c>
+      <c r="AP119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599724/statistics</t>
+        </is>
+      </c>
+      <c r="AQ119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
@@ -24333,6 +25077,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599833/statistics</t>
         </is>
       </c>
+      <c r="AP120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599833/statistics</t>
+        </is>
+      </c>
+      <c r="AQ120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -24464,6 +25214,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599833/statistics</t>
         </is>
       </c>
+      <c r="AP121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599833/statistics</t>
+        </is>
+      </c>
+      <c r="AQ121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -24599,6 +25355,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599892/statistics</t>
         </is>
       </c>
+      <c r="AP122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599892/statistics</t>
+        </is>
+      </c>
+      <c r="AQ122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -24734,6 +25496,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599892/statistics</t>
         </is>
       </c>
+      <c r="AP123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599892/statistics</t>
+        </is>
+      </c>
+      <c r="AQ123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
@@ -24869,6 +25637,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599879/statistics</t>
         </is>
       </c>
+      <c r="AP124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599879/statistics</t>
+        </is>
+      </c>
+      <c r="AQ124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -25004,6 +25778,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599879/statistics</t>
         </is>
       </c>
+      <c r="AP125" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599879/statistics</t>
+        </is>
+      </c>
+      <c r="AQ125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
@@ -25139,6 +25919,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599898/statistics</t>
         </is>
       </c>
+      <c r="AP126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599898/statistics</t>
+        </is>
+      </c>
+      <c r="AQ126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -25274,6 +26060,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599898/statistics</t>
         </is>
       </c>
+      <c r="AP127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599898/statistics</t>
+        </is>
+      </c>
+      <c r="AQ127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -25409,6 +26201,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599904/statistics</t>
         </is>
       </c>
+      <c r="AP128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599904/statistics</t>
+        </is>
+      </c>
+      <c r="AQ128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -25544,6 +26342,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599904/statistics</t>
         </is>
       </c>
+      <c r="AP129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599904/statistics</t>
+        </is>
+      </c>
+      <c r="AQ129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
@@ -25679,6 +26483,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599895/statistics</t>
         </is>
       </c>
+      <c r="AP130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599895/statistics</t>
+        </is>
+      </c>
+      <c r="AQ130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
@@ -25814,6 +26624,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599895/statistics</t>
         </is>
       </c>
+      <c r="AP131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599895/statistics</t>
+        </is>
+      </c>
+      <c r="AQ131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -25945,6 +26761,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599884/statistics</t>
         </is>
       </c>
+      <c r="AP132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599884/statistics</t>
+        </is>
+      </c>
+      <c r="AQ132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
@@ -26076,6 +26898,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599884/statistics</t>
         </is>
       </c>
+      <c r="AP133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599884/statistics</t>
+        </is>
+      </c>
+      <c r="AQ133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
@@ -26211,6 +27039,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599886/statistics</t>
         </is>
       </c>
+      <c r="AP134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599886/statistics</t>
+        </is>
+      </c>
+      <c r="AQ134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
@@ -26346,6 +27180,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599886/statistics</t>
         </is>
       </c>
+      <c r="AP135" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599886/statistics</t>
+        </is>
+      </c>
+      <c r="AQ135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -26481,6 +27321,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599901/statistics</t>
         </is>
       </c>
+      <c r="AP136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599901/statistics</t>
+        </is>
+      </c>
+      <c r="AQ136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -26616,6 +27462,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599901/statistics</t>
         </is>
       </c>
+      <c r="AP137" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599901/statistics</t>
+        </is>
+      </c>
+      <c r="AQ137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
@@ -26751,6 +27603,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599881/statistics</t>
         </is>
       </c>
+      <c r="AP138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599881/statistics</t>
+        </is>
+      </c>
+      <c r="AQ138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -26886,6 +27744,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599881/statistics</t>
         </is>
       </c>
+      <c r="AP139" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599881/statistics</t>
+        </is>
+      </c>
+      <c r="AQ139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
@@ -27017,6 +27881,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599889/statistics</t>
         </is>
       </c>
+      <c r="AP140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599889/statistics</t>
+        </is>
+      </c>
+      <c r="AQ140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
@@ -27148,6 +28018,12 @@
           <t>https://www.sofascore.com/api/v1/event/16599889/statistics</t>
         </is>
       </c>
+      <c r="AP141" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599889/statistics</t>
+        </is>
+      </c>
+      <c r="AQ141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -27273,6 +28149,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
@@ -27398,6 +28280,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP143" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
@@ -27527,6 +28415,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -27656,6 +28550,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
@@ -27781,6 +28681,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
@@ -27906,6 +28812,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
@@ -28031,6 +28943,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
@@ -28156,6 +29074,12 @@
           <t>https://www.sofascore.com/</t>
         </is>
       </c>
+      <c r="AP149" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/</t>
+        </is>
+      </c>
+      <c r="AQ149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -28287,6 +29211,12 @@
           <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
         </is>
       </c>
+      <c r="AP150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -28418,6 +29348,12 @@
           <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
         </is>
       </c>
+      <c r="AP151" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/algeciras-cf-hercules-cf/ChbsOOb#id:16599924,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -28549,6 +29485,12 @@
           <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
         </is>
       </c>
+      <c r="AP152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
@@ -28680,6 +29622,12 @@
           <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
         </is>
       </c>
+      <c r="AP153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/antequera-real-madrid-castilla-u21/ubcsyLj#id:16599937,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
@@ -28807,6 +29755,12 @@
           <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
         </is>
       </c>
+      <c r="AP154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
@@ -28934,6 +29888,12 @@
           <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
         </is>
       </c>
+      <c r="AP155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/atletico-madrileno-gimnastic-de-tarragona/PgbsBLj#id:16599934,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -29061,6 +30021,12 @@
           <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
         </is>
       </c>
+      <c r="AP156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
@@ -29188,6 +30154,12 @@
           <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
         </is>
       </c>
+      <c r="AP157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/juventud-torremolinos-cf-ue-sant-andreu-u19/nMjshtfc#id:16599940,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -29315,6 +30287,12 @@
           <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
         </is>
       </c>
+      <c r="AP158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
@@ -29442,6 +30420,12 @@
           <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
         </is>
       </c>
+      <c r="AP159" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es-la/football/match/rayo-majadahonda-real-jaen/QgbszQFb#id:16599928,tab:statistics</t>
+        </is>
+      </c>
+      <c r="AQ159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
@@ -29569,6 +30553,12 @@
           <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
         </is>
       </c>
+      <c r="AP160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+      <c r="AQ160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
@@ -29696,9 +30686,15 @@
           <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
         </is>
       </c>
+      <c r="AP161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/es/football/match/real-murcia-real-zaragoza/pgbsMOb</t>
+        </is>
+      </c>
+      <c r="AQ161" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO161"/>
+  <autoFilter ref="A1:AQ161"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO3" r:id="rId2"/>
@@ -33132,7 +34128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33959,7 +34955,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Resuelto el 20-10-2026: J8 completa mediante capturas y texto de Sofascore aportados por el usuario. 80 partidos en grupo2_partidos.csv; 77 con xG por tres ausencias antiguas.</t>
+          <t>J8 completa; 80 partidos. Revisión histórica 20-10-2026: 79 con xG (77 Sofascore + 2 complementarios identificados); Huesca–Sant Andreu pendiente.</t>
         </is>
       </c>
     </row>
@@ -34119,7 +35115,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Resuelto el 20-10-2026: J8 completa mediante capturas y texto de Sofascore aportados por el usuario. 80 partidos en grupo2_partidos.csv; 77 con xG por tres ausencias antiguas.</t>
+          <t>J8 completa; 80 partidos. Revisión histórica 20-10-2026: 79 con xG (77 Sofascore + 2 complementarios identificados); Huesca–Sant Andreu pendiente.</t>
         </is>
       </c>
     </row>
@@ -34143,8 +35139,68 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>xG Huesca–Sant Andreu</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>No se ha localizado xG fiable tras comprobar Sofascore, FotMob, ScanGoal y Atlético Stats</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Se mantiene ausente; no se usan predicciones previas ni cifras inconsistentes. Revisión 20-10-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>xG recuperados J2 y J5</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Dos partidos sin xG en Sofascore</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Recuperados 0.93–2.07 y 0.52–2.19 de ScanGoal/nb-bet; modelo no identificado. Fuente por fila y tabla solo Sofascore conservadas. Cobertura combinada 79/80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Libro con extracciones hasta J7</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Actualizadas las cuatro extracciones Hyper y el Excel interno a J8; 8 partidos, 25 jugadores, 20 equipos y 128 registros de minutos. Publicación en Tableau Public es independiente del archivo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D50"/>
+  <autoFilter ref="A1:D53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41398,7 +42454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -43252,22 +44308,22 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ocasiones_claras</t>
+          <t>fuente_xg</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Ocasiones claras (big chances).</t>
+          <t>URL específica del xG; puede diferir de la fuente del resto de estadísticas.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
         </is>
       </c>
     </row>
@@ -43279,22 +44335,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ocasiones_claras_rival</t>
+          <t>nota_xg</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Lo mismo, del rival.</t>
+          <t>Limitación del proveedor o modelo de los xG complementarios.</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Fuente complementaria; proveedor/modelo de xG no confirma…</t>
         </is>
       </c>
     </row>
@@ -43306,12 +44362,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>tiros</t>
+          <t>ocasiones_claras</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Tiros totales.</t>
+          <t>Ocasiones claras (big chances).</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -43321,7 +44377,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -43333,7 +44389,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>tiros_rival</t>
+          <t>ocasiones_claras_rival</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -43348,7 +44404,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -43360,12 +44416,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>tiros_a_puerta</t>
+          <t>tiros</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Tiros entre los tres palos.</t>
+          <t>Tiros totales.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -43375,7 +44431,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -43387,7 +44443,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>tiros_a_puerta_rival</t>
+          <t>tiros_rival</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -43402,7 +44458,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -43414,12 +44470,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>tiros_dentro_area</t>
+          <t>tiros_a_puerta</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Tiros desde dentro del área.</t>
+          <t>Tiros entre los tres palos.</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -43429,7 +44485,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -43441,7 +44497,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>tiros_dentro_area_rival</t>
+          <t>tiros_a_puerta_rival</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -43456,7 +44512,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -43468,12 +44524,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>posesion_pct</t>
+          <t>tiros_dentro_area</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Posesión, en %.</t>
+          <t>Tiros desde dentro del área.</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -43483,7 +44539,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -43495,7 +44551,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>posesion_pct_rival</t>
+          <t>tiros_dentro_area_rival</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -43510,7 +44566,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -43522,12 +44578,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>pases</t>
+          <t>posesion_pct</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Pases intentados.</t>
+          <t>Posesión, en %.</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -43537,7 +44593,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -43549,7 +44605,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>pases_rival</t>
+          <t>posesion_pct_rival</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -43564,7 +44620,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -43576,12 +44632,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>pases_buenos</t>
+          <t>pases</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Pases completados.</t>
+          <t>Pases intentados.</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -43591,7 +44647,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>524</t>
         </is>
       </c>
     </row>
@@ -43603,7 +44659,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>pases_buenos_rival</t>
+          <t>pases_rival</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -43618,7 +44674,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -43630,12 +44686,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>corners</t>
+          <t>pases_buenos</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Saques de esquina.</t>
+          <t>Pases completados.</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -43645,7 +44701,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>459</t>
         </is>
       </c>
     </row>
@@ -43657,7 +44713,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>corners_rival</t>
+          <t>pases_buenos_rival</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -43672,7 +44728,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -43684,12 +44740,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>faltas</t>
+          <t>corners</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Faltas cometidas.</t>
+          <t>Saques de esquina.</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -43699,7 +44755,7 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -43711,7 +44767,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>faltas_rival</t>
+          <t>corners_rival</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -43726,7 +44782,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -43738,12 +44794,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>amarillas</t>
+          <t>faltas</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Tarjetas amarillas.</t>
+          <t>Faltas cometidas.</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -43753,7 +44809,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -43765,7 +44821,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>amarillas_rival</t>
+          <t>faltas_rival</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -43780,7 +44836,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -43792,12 +44848,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>rojas</t>
+          <t>amarillas</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Tarjetas rojas.</t>
+          <t>Tarjetas amarillas.</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -43807,7 +44863,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -43819,7 +44875,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>rojas_rival</t>
+          <t>amarillas_rival</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -43834,7 +44890,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -43846,12 +44902,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>duelos_ganados_pct</t>
+          <t>rojas</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Duelos ganados, en %.</t>
+          <t>Tarjetas rojas.</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -43861,7 +44917,7 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -43873,7 +44929,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>duelos_ganados_pct_rival</t>
+          <t>rojas_rival</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -43888,7 +44944,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -43900,12 +44956,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>entradas_ultimo_tercio</t>
+          <t>duelos_ganados_pct</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Entradas al último tercio del campo.</t>
+          <t>Duelos ganados, en %.</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -43915,7 +44971,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -43927,7 +44983,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>entradas_ultimo_tercio_rival</t>
+          <t>duelos_ganados_pct_rival</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -43942,7 +44998,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -43954,12 +45010,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>recuperaciones</t>
+          <t>entradas_ultimo_tercio</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Recuperaciones de balón.</t>
+          <t>Entradas al último tercio del campo.</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -43969,7 +45025,7 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -43981,7 +45037,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>recuperaciones_rival</t>
+          <t>entradas_ultimo_tercio_rival</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -43996,7 +45052,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -44008,12 +45064,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>paradas</t>
+          <t>recuperaciones</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Paradas del portero.</t>
+          <t>Recuperaciones de balón.</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -44023,7 +45079,7 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -44035,7 +45091,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>paradas_rival</t>
+          <t>recuperaciones_rival</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -44050,7 +45106,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -44062,39 +45118,39 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>paradas</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
+          <t>Paradas del portero.</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>clasificacion</t>
+          <t>grupo2_partidos</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>tras_jornada</t>
+          <t>paradas_rival</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Jornada después de la cual se toma la clasificación.</t>
+          <t>Lo mismo, del rival.</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -44111,27 +45167,27 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>clasificacion</t>
+          <t>grupo2_partidos</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>posicion</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Puesto en la tabla.</t>
+          <t>Dirección de la API de Sofascore de la que copié el dato.</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://www.sofascore.com/api/v1/event/16599360/statistics</t>
         </is>
       </c>
     </row>
@@ -44143,22 +45199,22 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>equipo</t>
+          <t>tras_jornada</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Equipo.</t>
+          <t>Jornada después de la cual se toma la clasificación.</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -44170,12 +45226,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>pj</t>
+          <t>posicion</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Partidos jugados.</t>
+          <t>Puesto en la tabla.</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -44185,7 +45241,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -44197,22 +45253,22 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Partidos ganados.</t>
+          <t>Equipo.</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
     </row>
@@ -44224,12 +45280,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>pj</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Partidos empatados.</t>
+          <t>Partidos jugados.</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -44239,7 +45295,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -44251,12 +45307,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Partidos perdidos.</t>
+          <t>Partidos ganados.</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -44266,7 +45322,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -44278,12 +45334,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>gf</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Goles a favor.</t>
+          <t>Partidos empatados.</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -44293,7 +45349,7 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -44305,12 +45361,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>gc</t>
+          <t>p</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Goles en contra.</t>
+          <t>Partidos perdidos.</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -44320,7 +45376,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -44332,12 +45388,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>puntos</t>
+          <t>gf</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Puntos.</t>
+          <t>Goles a favor.</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -44347,7 +45403,7 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -44359,39 +45415,39 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>gc</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Goles en contra.</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>proximos</t>
+          <t>clasificacion</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>puntos</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Puntos.</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -44401,24 +45457,24 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>proximos</t>
+          <t>clasificacion</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>competicion</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Competición.</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -44428,7 +45484,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Primera Federación</t>
+          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
         </is>
       </c>
     </row>
@@ -44440,22 +45496,22 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Fecha prevista (puede cambiar).</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -44467,12 +45523,12 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>competicion</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>«Casa» o «Fuera».</t>
+          <t>Competición.</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -44482,7 +45538,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>Primera Federación</t>
         </is>
       </c>
     </row>
@@ -44494,12 +45550,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>Fecha prevista (puede cambiar).</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -44509,7 +45565,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -44521,12 +45577,12 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>«Casa» o «Fuera».</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -44536,24 +45592,24 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
+          <t>Fuera</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>partidos_rivales</t>
+          <t>proximos</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>equipo</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Equipo del que son los resultados.</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -44563,34 +45619,34 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CE Europa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>partidos_rivales</t>
+          <t>proximos</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
         </is>
       </c>
     </row>
@@ -44602,12 +45658,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Fecha.</t>
+          <t>Equipo del que son los resultados.</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -44617,7 +45673,7 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>Real Murcia</t>
         </is>
       </c>
     </row>
@@ -44629,22 +45685,22 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Equipo local.</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Hércules</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -44656,12 +45712,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>visitante</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Equipo visitante.</t>
+          <t>Fecha.</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -44671,7 +45727,7 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -44683,22 +45739,22 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>goles_local</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Goles del local.</t>
+          <t>Equipo local.</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Hércules</t>
         </is>
       </c>
     </row>
@@ -44710,22 +45766,22 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>goles_visitante</t>
+          <t>visitante</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Goles del visitante.</t>
+          <t>Equipo visitante.</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Real Murcia</t>
         </is>
       </c>
     </row>
@@ -44737,39 +45793,39 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>fuente_url</t>
+          <t>goles_local</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Página de la que saqué el dato.</t>
+          <t>Goles del local.</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://futbolme.com/resultados-directo/equipo/real-murci…</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>incidencias</t>
+          <t>partidos_rivales</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>goles_visitante</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Jornada afectada (0 si afecta a todo el proyecto).</t>
+          <t>Goles del visitante.</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -44779,24 +45835,24 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>incidencias</t>
+          <t>partidos_rivales</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>fuente_url</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Dato o tabla afectada.</t>
+          <t>Página de la que saqué el dato.</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -44806,7 +45862,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>https://futbolme.com/resultados-directo/equipo/real-murci…</t>
         </is>
       </c>
     </row>
@@ -44818,22 +45874,22 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>problema</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Qué no cuadra.</t>
+          <t>Jornada afectada (0 si afecta a todo el proyecto).</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>No hay datos públicos fiables de coordenadas, tracking, d…</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -44845,12 +45901,12 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>campo</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Qué he hecho con ello.</t>
+          <t>Dato o tabla afectada.</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -44860,24 +45916,24 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>No se estiman ni se rellenan</t>
+          <t>Cobertura</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>goles_video</t>
+          <t>incidencias</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>gol_id</t>
+          <t>problema</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Jornada y número de gol del partido (6-02 = segundo gol de la J6).</t>
+          <t>Qué no cuadra.</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -44887,34 +45943,34 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>1-01</t>
+          <t>No hay datos públicos fiables de coordenadas, tracking, d…</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>goles_video</t>
+          <t>incidencias</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Qué he hecho con ello.</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No se estiman ni se rellenan</t>
         </is>
       </c>
     </row>
@@ -44926,22 +45982,22 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>gol_id</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Jornada de liga.</t>
+          <t>Jornada y número de gol del partido (6-02 = segundo gol de la J6).</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-01</t>
         </is>
       </c>
     </row>
@@ -44953,22 +46009,22 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -44980,22 +46036,22 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>«Casa» o «Fuera».</t>
+          <t>Jornada de liga.</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -45007,12 +46063,12 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>sentido</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>«Favor» o «Contra».</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -45022,7 +46078,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Contra</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
     </row>
@@ -45034,12 +46090,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Minuto en texto, con el descuento (45+7).</t>
+          <t>«Casa» o «Fuera».</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -45049,7 +46105,7 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Fuera</t>
         </is>
       </c>
     </row>
@@ -45061,12 +46117,12 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>marcador</t>
+          <t>sentido</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Resultado justo después del gol, siempre Zaragoza-rival.</t>
+          <t>«Favor» o «Contra».</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -45076,7 +46132,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>Contra</t>
         </is>
       </c>
     </row>
@@ -45088,12 +46144,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>goleador</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Quién marca.</t>
+          <t>Minuto en texto, con el descuento (45+7).</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -45103,7 +46159,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Sinan Bakis</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -45115,12 +46171,12 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>asistencia</t>
+          <t>marcador</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Quién da el último pase, si consta.</t>
+          <t>Resultado justo después del gol, siempre Zaragoza-rival.</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -45130,7 +46186,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
@@ -45142,12 +46198,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>inicio</t>
+          <t>goleador</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Cómo empieza la jugada: ataque posicional, transición, balón parado, penalti o sin dato.</t>
+          <t>Quién marca.</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -45157,7 +46213,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>balon_parado</t>
+          <t>Sinan Bakis</t>
         </is>
       </c>
     </row>
@@ -45169,12 +46225,12 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>detalle_inicio</t>
+          <t>asistencia</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>La misma idea en una frase corta.</t>
+          <t>Quién da el último pase, si consta.</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -45184,7 +46240,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>falta lateral</t>
+          <t>Jaume Jardí</t>
         </is>
       </c>
     </row>
@@ -45196,12 +46252,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>carril</t>
+          <t>inicio</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Izquierda, centro o derecha DEL EQUIPO QUE ATACA.</t>
+          <t>Cómo empieza la jugada: ataque posicional, transición, balón parado, penalti o sin dato.</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -45211,7 +46267,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>derecha</t>
+          <t>balon_parado</t>
         </is>
       </c>
     </row>
@@ -45223,12 +46279,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>ultimo_pase</t>
+          <t>detalle_inicio</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Tipo de último pase: centro lateral, pase atrás, pase raso por dentro, al espacio, rechace, córner, falta…</t>
+          <t>La misma idea en una frase corta.</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -45238,7 +46294,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>falta_lateral</t>
+          <t>falta lateral</t>
         </is>
       </c>
     </row>
@@ -45250,12 +46306,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>zona_remate</t>
+          <t>carril</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Zona del último toque: área pequeña, área grande (centro o lateral), fuera del área o penalti.</t>
+          <t>Izquierda, centro o derecha DEL EQUIPO QUE ATACA.</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -45265,7 +46321,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>area_pequena</t>
+          <t>derecha</t>
         </is>
       </c>
     </row>
@@ -45277,12 +46333,12 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>remate</t>
+          <t>ultimo_pase</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Con qué se remata: pie, cabeza o propia puerta.</t>
+          <t>Tipo de último pase: centro lateral, pase atrás, pase raso por dentro, al espacio, rechace, córner, falta…</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -45292,7 +46348,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>sin_dato</t>
+          <t>falta_lateral</t>
         </is>
       </c>
     </row>
@@ -45304,12 +46360,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>revision_fvs</t>
+          <t>zona_remate</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Si se ve una revisión en el monitor (FVS).</t>
+          <t>Zona del último toque: área pequeña, área grande (centro o lateral), fuera del área o penalti.</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -45319,7 +46375,7 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>no_se_ve</t>
+          <t>area_pequena</t>
         </is>
       </c>
     </row>
@@ -45331,22 +46387,22 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>defensores_area</t>
+          <t>remate</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Defensores dentro del área en el momento del último pase, solo si se ven todos.</t>
+          <t>Con qué se remata: pie, cabeza o propia puerta.</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>sin_dato</t>
         </is>
       </c>
     </row>
@@ -45358,22 +46414,22 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>atacantes_area</t>
+          <t>revision_fvs</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Atacantes dentro del área en ese mismo momento.</t>
+          <t>Si se ve una revisión en el monitor (FVS).</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no_se_ve</t>
         </is>
       </c>
     </row>
@@ -45385,12 +46441,12 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>tiro_x</t>
+          <t>defensores_area</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Posición estimada del remate, en metros hacia la portería rival (0 a 105).</t>
+          <t>Defensores dentro del área en el momento del último pase, solo si se ven todos.</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -45400,7 +46456,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -45412,12 +46468,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>tiro_y</t>
+          <t>atacantes_area</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Posición estimada del remate, en metros desde la banda derecha del que ataca (0 a 68).</t>
+          <t>Atacantes dentro del área en ese mismo momento.</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -45427,7 +46483,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -45439,12 +46495,12 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>pase_x</t>
+          <t>tiro_x</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Posición estimada del último pase (x).</t>
+          <t>Posición estimada del remate, en metros hacia la portería rival (0 a 105).</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -45454,7 +46510,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -45466,12 +46522,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>pase_y</t>
+          <t>tiro_y</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Posición estimada del último pase (y).</t>
+          <t>Posición estimada del remate, en metros desde la banda derecha del que ataca (0 a 68).</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -45481,7 +46537,7 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -45493,22 +46549,22 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>segundos_video</t>
+          <t>pase_x</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Dónde está la jugada en el resumen, en segundos.</t>
+          <t>Posición estimada del último pase (x).</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -45520,22 +46576,22 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>confianza</t>
+          <t>pase_y</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Alta, media o baja: lo bien que se ve la jugada.</t>
+          <t>Posición estimada del último pase (y).</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -45547,12 +46603,12 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>segundos_video</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Lo que se ve en el vídeo, explicado en una o dos frases.</t>
+          <t>Dónde está la jugada en el resumen, en segundos.</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -45562,61 +46618,61 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Falta desde la derecha del ataque del Nàstic. El balón ca…</t>
+          <t>17-26</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>resumenes_youtube</t>
+          <t>goles_video</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>confianza</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Alta, media o baja: lo bien que se ve la jugada.</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>media</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>resumenes_youtube</t>
+          <t>goles_video</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Jornada.</t>
+          <t>Lo que se ve en el vídeo, explicado en una o dos frases.</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Falta desde la derecha del ataque del Nàstic. El balón ca…</t>
         </is>
       </c>
     </row>
@@ -45628,22 +46684,22 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>rival</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Rival.</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -45655,22 +46711,22 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Canal de YouTube que publica el resumen.</t>
+          <t>Jornada.</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Real Federación Española Fútbol</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -45682,12 +46738,12 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>rival</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Título del vídeo.</t>
+          <t>Rival.</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -45697,7 +46753,7 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Resumen #PrimeraFederación | Gimnàstic 2-0 Real Zaragoza …</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
     </row>
@@ -45709,12 +46765,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>duracion</t>
+          <t>canal</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Duración (minutos:segundos).</t>
+          <t>Canal de YouTube que publica el resumen.</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -45724,7 +46780,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>4:03</t>
+          <t>Real Federación Española Fútbol</t>
         </is>
       </c>
     </row>
@@ -45736,12 +46792,12 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>titulo</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Enlace al vídeo.</t>
+          <t>Título del vídeo.</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -45751,24 +46807,24 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=psvkPAyTRhk</t>
+          <t>Resumen #PrimeraFederación | Gimnàstic 2-0 Real Zaragoza …</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>jugadores</t>
+          <t>resumenes_youtube</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>jugador</t>
+          <t>duracion</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Jugador.</t>
+          <t>Duración (minutos:segundos).</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -45778,34 +46834,34 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>4:03</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>jugadores</t>
+          <t>resumenes_youtube</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>partidos</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Partidos jugados.</t>
+          <t>Enlace al vídeo.</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>https://www.youtube.com/watch?v=psvkPAyTRhk</t>
         </is>
       </c>
     </row>
@@ -45817,22 +46873,22 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>titularidades</t>
+          <t>jugador</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Partidos como titular.</t>
+          <t>Jugador.</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Jaume Jardí</t>
         </is>
       </c>
     </row>
@@ -45844,12 +46900,12 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>minutos</t>
+          <t>partidos</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Minutos jugados, sin contar el descuento.</t>
+          <t>Partidos jugados.</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -45859,7 +46915,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -45871,12 +46927,12 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>goles</t>
+          <t>titularidades</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Goles.</t>
+          <t>Partidos como titular.</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -45886,7 +46942,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -45898,12 +46954,12 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>asistencias</t>
+          <t>minutos</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Asistencias (solo las que constan).</t>
+          <t>Minutos jugados, sin contar el descuento.</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -45913,7 +46969,7 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>639</t>
         </is>
       </c>
     </row>
@@ -45925,12 +46981,12 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>participaciones_con_minutos</t>
+          <t>goles</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Goles + asistencias.</t>
+          <t>Goles.</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -45940,7 +46996,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -45952,22 +47008,22 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>participaciones_por_90</t>
+          <t>asistencias</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Goles + asistencias por cada 90 minutos jugados.</t>
+          <t>Asistencias (solo las que constan).</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Número decimal</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -45979,12 +47035,12 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>minutos_por_participacion</t>
+          <t>participaciones_con_minutos</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Minutos que tarda de media en participar en un gol. Vacío si no ha participado en ninguno.</t>
+          <t>Goles + asistencias.</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -45994,61 +47050,61 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>minutos_partido</t>
+          <t>jugadores</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>partido_id</t>
+          <t>participaciones_por_90</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Partido (ver tabla partidos).</t>
+          <t>Goles + asistencias por cada 90 minutos jugados.</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Número decimal</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.13</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>minutos_partido</t>
+          <t>jugadores</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>jugador</t>
+          <t>minutos_por_participacion</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Jugador.</t>
+          <t>Minutos que tarda de media en participar en un gol. Vacío si no ha participado en ninguno.</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Westerveld</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -46060,22 +47116,22 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>rol</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>«Titular» o «Suplente».</t>
+          <t>Partido (ver tabla partidos).</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Número entero</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -46087,22 +47143,22 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>entra</t>
+          <t>jugador</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Minuto en el que entra (0 si es titular).</t>
+          <t>Jugador.</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Westerveld</t>
         </is>
       </c>
     </row>
@@ -46114,22 +47170,22 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>sale</t>
+          <t>rol</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Minuto en el que sale (90 si acaba el partido).</t>
+          <t>«Titular» o «Suplente».</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Número entero</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Titular</t>
         </is>
       </c>
     </row>
@@ -46141,27 +47197,81 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
+          <t>entra</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Minuto en el que entra (0 si es titular).</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Número entero</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>minutos_partido</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Minuto en el que sale (90 si acaba el partido).</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>Número entero</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>minutos_partido</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
           <t>minutos</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>Minutos jugados.</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D178" s="4" t="inlineStr">
         <is>
           <t>Número entero</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E176"/>
+  <autoFilter ref="A1:E178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -41,7 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -34128,7 +34128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35199,8 +35199,28 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>xPts sin xG</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Sustituir el xPts ausente por puntos reales oculta la ausencia y mezcla datos con resultados</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Corregido 20-10-2026: xPts queda ausente. Se comparan solo puntos reales y esperados de los mismos partidos con xG; cobertura 7/8 para Huesca y Sant Andreu.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D53"/>
+  <autoFilter ref="A1:D54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -41,7 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -34128,7 +34128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35219,8 +35219,28 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Horario y TV J9</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Sofascore (team/next) daba 25-10 16:00 UTC y aún mostraba la J8 sin jugar; respuesta desactualizada</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Se mantiene 23-10 19:15 UTC (21:15 hora local), confirmado por Movistar Plus+, Aragón Digital y Sport Aragón. TV: solo canales citados en al menos dos fuentes; Orange y Embou, en una sola, no se incluyen.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D54"/>
+  <autoFilter ref="A1:D55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -29,23 +29,23 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AQ$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'minutos_partido'!$A$1:$F$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'minutos_partido'!$A$1:$F$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -33354,7 +33354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33399,7 +33399,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -33408,17 +33408,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Villarreal B</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -33429,7 +33429,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -33448,7 +33448,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Villarreal B</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -33457,42 +33457,11 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Primera Federación</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>SD Huesca</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.fotmob.com/es-419/teams/8394/overview</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33504,10 +33473,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -34099,8 +34068,296 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599366/statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599697/statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/api/v1/event/16599875/statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fotmob.com/es/teams/161771/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Atlético Madrileño</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fotmob.com/es/teams/161771/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fotmob.com/es/teams/161771/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fotmob.com/es/teams/161771/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>CD Teruel</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.fotmob.com/es/teams/161771/overview</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -34117,6 +34374,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34128,7 +34393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35239,8 +35504,168 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Gol</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>La web del club (noticia) y Sport Aragón atribuyen el gol del 80 a Diego González; la ficha oficial del club, FotMob, futboltotal y Aragón Digital lo dan en propia puerta de Álex Cano</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Uso la ficha oficial: propia puerta de Álex Cano en el 80 (Sport Aragón da 79 en la crónica). Sin asistencia; el córner lo sacó Rubén Díez</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Cambios</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Aragón Digital empareja Rubén Díez por Ureña (56) y Cuenca por Pereira (78); Sport Aragón da 55 y 77</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Uso la ficha oficial, que coincide con futboltotal: Rubén Díez por Saidu y Pau Sans por Ureña (56), Joaquín por Ander (65), Tobajas por Pereira y Cuenca por Jardí (78); los minutos jugados no cambian</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Tiros</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Ficha oficial: 9-8 tiros y 2-1 a puerta, con desglose que no suma; 365Scores: 10-8 y 3-1. BeSoccer no accesible desde la lectura web (24-10-2026)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Uso el club y marco el desglose como incompleto; posesión 67-33 coincide en club y 365Scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Estadísticas del club</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>La ficha oficial muestra ceros en córners, faltas, tarjetas, paradas y duelos que contradicen los eventos</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>No uso esos ceros; solo posesión y pases. Fueras de juego (2-2) marcados como dudosos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Sofascore</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Las lecturas web de event/16599975/statistics e incidents fallan, y event/16599975 devolvía el partido sin jugar (24-10-2026)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Sin métricas de Sofascore ni xG de la J9; queda pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Solo se ha jugado CE Europa–Real Zaragoza de la J9 (resto, 24 y 25-10). Tabla del club: Zaragoza 1.º con 20 puntos y 9 PJ</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Mantengo clasificacion.csv tras la J8 completa; la tras J9 se añade cuando termine la jornada</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>J9 en curso: solo CE Europa–Real Zaragoza terminado (resto, 24 y 25-10); Sofascore no accesible desde la lectura web</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>No añado filas a grupo2_partidos.csv hasta poder leer las estadísticas ALL; el grupo sigue con 80 partidos (J1-J8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Previa Villarreal B</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Futbolme y BeSoccer no accesibles; FotMob solo muestra los cinco últimos partidos (J4-J8)</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>J4-J8 contrastadas entre FotMob y grupo2_partidos.csv (Sofascore); J1-J3 solo Sofascore, con balance total (17-9, 17 puntos) igual a la clasificación oficial tras la J8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D55"/>
+  <autoFilter ref="A1:D63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38635,62 +39060,62 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>Westerveld</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>639</v>
+        <v>720</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>80</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Westerveld</t>
+          <t>Jaume Jardí</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>630</v>
+        <v>717</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -38699,13 +39124,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>612</v>
+        <v>702</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>2</v>
@@ -38717,10 +39142,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>306</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -38730,13 +39155,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="D5" s="5" t="n">
-        <v>606</v>
+        <v>696</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -38759,13 +39184,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>601</v>
+        <v>691</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
@@ -38777,10 +39202,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>300</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -38790,13 +39215,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>528</v>
+        <v>618</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -38815,17 +39240,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>P. Ademo</t>
+          <t>Raúl Pereira</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -38844,17 +39269,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Raúl Pereira</t>
+          <t>P. Ademo</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -38873,62 +39298,62 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Óscar Ureña</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n"/>
+        <v>0.86</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Óscar Ureña</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -38937,13 +39362,13 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -38955,10 +39380,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>354</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13">
@@ -38968,13 +39393,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1</v>
@@ -38986,55 +39411,57 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>300</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Iker Vadillo</t>
+          <t>Edu Espiau</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n"/>
+        <v>1.36</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>S. Escudero</t>
+          <t>Ander Herrera</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -39053,17 +39480,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ander Herrera</t>
+          <t>Iker Vadillo</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="D16" s="4" t="n">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
@@ -39082,33 +39509,31 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Edu Espiau</t>
+          <t>S. Escudero</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D17" s="5" t="n">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -39142,53 +39567,57 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>H. Barrachina</t>
+          <t>Yussif Saidu</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Yussif Saidu</t>
+          <t>H. Barrachina</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
@@ -39200,13 +39629,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -39277,17 +39706,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Diego Monzón</t>
+          <t>J. Tobajas</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
@@ -39304,7 +39733,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>J. Tobajas</t>
+          <t>Diego Monzón</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -39367,7 +39796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42482,8 +42911,392 @@
         <v>5</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Westerveld</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Marco Sangalli</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Rubo</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Diego González</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Raúl Pereira</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Lucas Terrer</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Edu Espiau</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Rubén Díez</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>J. Tobajas</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Marcos Cuenca</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Suplente</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F129"/>
+  <autoFilter ref="A1:F145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45551,7 +46364,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -45605,7 +46418,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -45632,7 +46445,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Fuera</t>
+          <t>Casa</t>
         </is>
       </c>
     </row>
@@ -45659,7 +46472,7 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Villarreal B</t>
         </is>
       </c>
     </row>
@@ -46928,7 +47741,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Jaume Jardí</t>
+          <t>Westerveld</t>
         </is>
       </c>
     </row>
@@ -46982,7 +47795,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47822,7 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -47036,7 +47849,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -47063,7 +47876,7 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -47090,7 +47903,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -47117,7 +47930,7 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -47144,7 +47957,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -47322,7 +48135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47755,8 +48568,53 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Primera Federación</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -47766,6 +48624,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47777,7 +48636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48924,8 +49783,48 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Favor</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Álex Cano</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -48953,6 +49852,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48964,7 +49864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50309,8 +51209,173 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Westerveld</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Marco Sangalli</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Rubo</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Diego González</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Raúl Pereira</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Lucas Terrer</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Edu Espiau</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C89"/>
+  <autoFilter ref="A1:C100"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -50400,6 +51465,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50411,7 +51487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -51368,8 +52444,123 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Rubén Díez</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Óscar Ureña</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Ander Herrera</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>J. Tobajas</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Raúl Pereira</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Marcos Cuenca</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Jaume Jardí</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E41"/>
+  <autoFilter ref="A1:E46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -51411,6 +52602,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51422,7 +52618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52057,8 +53253,54 @@
         <v>87</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Lucas Terrer</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>J. Tobajas</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Amarilla</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E29"/>
+  <autoFilter ref="A1:E31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -52088,6 +53330,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52099,7 +53343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52109,7 +53353,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
@@ -52484,8 +53728,48 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Web del club (posesión igual en 365Scores)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>El club da 2 a puerta + 5 fuera + 0 bloqueados (no suman 9); 365Scores da 10-8 tiros y 3-1 a puerta</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -52495,6 +53779,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52506,7 +53791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57453,8 +58738,132 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>posesion_pct</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>pases</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>677</v>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>pases_completados</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>596</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>fueras_juego</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>dudosa</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-primera-federacion-9-ce-europa-vs-real-zaragoza-3940</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G159"/>
+  <autoFilter ref="A1:G163"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -57614,6 +59023,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -41,7 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -34393,7 +34393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35664,8 +35664,48 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Libro con extracciones hasta J8</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Actualizadas las cuatro extracciones Hyper y el Excel interno a J9 con actualizar_tableau.py (comprobaciones ya no fijas en la J8): 9 partidos, 25 jugadores, 20 equipos (clasificación tras la J8) y 27 goles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Vídeo y ocasiones</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Aragón Digital describe un tiro de Flavio al palo en el 10; Aragón Play, un disparo fuera en el 11; la ficha marca cero al palo (campo poco fiable)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>No se afirma el palo: se cita solo un disparo de Flavio en torno al 10. Revisión por secuencias del resumen (6:11) aportada por el usuario el 24-10-2026, sin minuto asignado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D63"/>
+  <autoFilter ref="A1:D65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -38,10 +38,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sofascore'!$A$1:$F$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AQ$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -30867,7 +30867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33280,8 +33280,788 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Real Jaén</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Gimnàstic</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Hércules</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Real Madrid Castilla</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Atlético Madrileño</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Sant Andreu</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Rayo Majadahonda</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>CDA Águilas FC</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>CE Europa</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Juventud Torremolinos CF</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>CD Teruel</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://es.besoccer.com/competicion/clasificacion/primera_division_rfef/2027/grupo2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K61"/>
+  <autoFilter ref="A1:K81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -33343,6 +34123,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33438,7 +34238,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -34393,7 +35193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35704,8 +36504,88 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>J9 completa el 25-10. BeSoccer (tabla tras la J9) coincide con la clasificación tras la J8 más los diez resultados de la J9 (El Periódico de Ceuta)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Añadida la clasificación tras la J9 con el orden de BeSoccer (Huesca 11.º y Castilla 12.º, empatados en puntos, diferencia y goles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>J9 completa (10 resultados, El Periódico de Ceuta, cuadran con BeSoccer); Sofascore sigue sin responder a la lectura web</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Añadidos los resultados a grupo2_resultados.csv; grupo2_partidos.csv sigue con J1-J8 (80 partidos) hasta poder leer las estadísticas ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Calendario</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>proximos.csv tenía el Real Zaragoza-SD Huesca el 08-11; la RFEF fijó el sábado 07-11 a las 21:00 (Sport Aragón 15-10, futboltotal y datos/sofascore.json)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Corregida la fecha a 2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>TV Copa</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>CD Tudelano-Real Zaragoza (27-10, 21:00, Municipal de Tudela): Aragón TV en abierto según Sport Aragón (26-10) y Aragón Digital (21-10)</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Añadido Aragón TV (abierto) a la lista tv de datos/sofascore.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D65"/>
+  <autoFilter ref="A1:D69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
+++ b/analisis/real-zaragoza/datos/tablas/datos_real_zaragoza.xlsx
@@ -29,10 +29,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diccionario'!$A$1:$E$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'partidos'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'goles'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'alineaciones'!$A$1:$C$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'cambios'!$A$1:$E$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tarjetas'!$A$1:$E$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tiros'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'estadisticas'!$A$1:$G$163</definedName>
@@ -40,8 +40,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'grupo2_partidos'!$A$1:$AQ$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'clasificacion'!$A$1:$K$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'proximos'!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'partidos_rivales'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'incidencias'!$A$1:$D$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'goles_video'!$A$1:$Z$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'resumenes_youtube'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'jugadores'!$A$1:$I$26</definedName>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -34273,7 +34273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35156,8 +35156,44 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Villarreal B</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.elperiodicodeceuta.es/resultados-primera-federacion-grupo-2-jornada-9-2026-27/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -35182,6 +35218,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35193,7 +35230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36584,8 +36621,148 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Minutos de los goles: ficha del club 12', 20' (penalti), 37' y 41'; Aragón Digital y Sport Aragón 11', 19', 36' y 40'. futboltotal da los dos goles de Pau Sans de penalti; el club, Aragón Digital y Sport Aragón solo el primero</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Se usan los minutos del club y solo el 0-2 como penalti</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Solo la ficha del club da asistencia (Marcos Cuenca en el 0-1). Aragón Digital describe un pase de Pau Sans en el 0-4 que el club no registra como asistencia</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Se apunta solo la asistencia del club</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Cambios</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Primer cambio del Zaragoza (Escudero por Raúl Pereira): 45' en la ficha del club, 46' en Aragón Digital y futboltotal; entra tras el descanso</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Se apunta en el 46'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Estadísticas</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>La ficha del club muestra ceros en todas las estadísticas del partido; Sport Aragón y Aragón Digital no publican estadísticas; Sofascore no responde desde la lectura web (client_error)</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Sin tiros, posesión ni estadísticas: se dejan vacías</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Tarjetas</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna tarjeta al Zaragoza en el club, Aragón Digital y futboltotal. La única amarilla es del Tudelano (Olartzabal 47' según el club; el entrenador según Aragón Digital)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Sin tarjetas del Zaragoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Real Zaragoza-Villarreal B: la ficha del club (31-10, 21:00, Ibercaja Estadio) y futbolenlatele coinciden; FotMob lo lista el domingo 1-11 a las 16:00 y el listado de Sofascore también el 1-11, pero ese listado sigue mostrando como no jugadas la J8 y la J9 (copia desactualizada)</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Se mantiene el sábado 31-10 a las 21:00 (club y futbolenlatele)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Solo futbolenlatele indica Aragón TV, Aragón Play y Movistar; el club no publica la emisión y no hay una segunda fuente para este partido</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>tv se deja vacía hasta tener dos fuentes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D69"/>
+  <autoFilter ref="A1:D76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49055,7 +49232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49533,8 +49710,51 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Copa del Rey</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>CD Tudelano</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -49545,6 +49765,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49556,7 +49777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50743,8 +50964,172 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Favor</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Marcos Cuenca</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Favor</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Favor</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Favor</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Hugo Pinilla</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -50773,6 +51158,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50784,7 +51173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52294,8 +52683,173 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Anartz Peña</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>J. Gabilondo</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Raúl Pereira</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>H. Barrachina</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Tachi</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Marcos Cuenca</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Pinilla</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Yussif Saidu</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Diego Monzón</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C100"/>
+  <autoFilter ref="A1:C111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -52396,6 +52950,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52407,7 +52972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53479,8 +54044,123 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>S. Escudero</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Raúl Pereira</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Lalo Arantegui</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>J. Gabilondo</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>J. Tobajas</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Pau Sans</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Laken Torres</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Sergio Beltrán</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Diego Monzón</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.realzaragoza.com/partidos/temporada-2026-2027-copa-del-rey-3-tudelano-vs-real-zaragoza-5218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E46"/>
+  <autoFilter ref="A1:E51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -53527,6 +54207,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
